--- a/Resultados_planta_custos_emissoes_hubs.xlsx
+++ b/Resultados_planta_custos_emissoes_hubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fce9e6a828229890/Meus artigos/Resíduos na produção de cimento/Waste in Cement Industry/Waste_cement/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epegovbr-my.sharepoint.com/personal/otto_hebeda_epe_gov_br/Documents/Documentos/Resíduos - projetos/Residuos na produção de cimento/Código/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_88B55A31088DCF73299E7AD3AB8741A67D8A8A46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DD86213-60BD-4D5B-BC93-4D98880DDD63}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_88B55A31088DCF73299E7AD3AB8741A67D8A8A46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FDB0AC7-46E5-43DA-9198-EB36E7C13FA3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raio" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,23 @@
     <sheet name="Resumo_Hubs" sheetId="3" r:id="rId3"/>
     <sheet name="Plantas_com_Hub" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Custos_Emissoes!$A$1:$U$65</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -515,7 +531,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,6 +547,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -561,17 +589,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1406,6 +1438,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1474,16 +1514,16 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B2">
-        <v>40</v>
-      </c>
-      <c r="C2">
-        <v>11285480.33622128</v>
+        <v>140</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1921115.320275252</v>
       </c>
       <c r="D2">
-        <v>1.452</v>
+        <v>5.0819999999999999</v>
       </c>
       <c r="E2">
         <v>11.942294831374801</v>
@@ -1492,63 +1532,63 @@
         <v>104.5</v>
       </c>
       <c r="G2">
-        <v>117.89429483137479</v>
+        <v>121.5242948313748</v>
       </c>
       <c r="H2">
-        <v>1330493746.072154</v>
-      </c>
-      <c r="I2">
-        <v>125609865.2115964</v>
+        <v>233462184.58620071</v>
+      </c>
+      <c r="I2" s="3">
+        <v>21382433.82173181</v>
       </c>
       <c r="J2">
-        <v>-1204883880.860558</v>
+        <v>-212079750.76446891</v>
       </c>
       <c r="K2">
         <v>200</v>
       </c>
       <c r="L2">
-        <v>56428</v>
+        <v>9606</v>
       </c>
       <c r="M2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="N2">
-        <v>4514240</v>
+        <v>2689680</v>
       </c>
       <c r="O2">
-        <v>1354272</v>
+        <v>806904</v>
       </c>
       <c r="P2">
-        <v>3615906.24</v>
-      </c>
-      <c r="Q2">
-        <v>1047292575.201335</v>
+        <v>2154433.6800000002</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>178279501.7215434</v>
       </c>
       <c r="R2">
-        <v>52364628.760066733</v>
-      </c>
-      <c r="S2">
-        <v>55980535.000066727</v>
-      </c>
-      <c r="T2">
-        <v>991312040.20126796</v>
+        <v>8913975.0860771704</v>
+      </c>
+      <c r="S2" s="3">
+        <v>11068408.7660772</v>
+      </c>
+      <c r="T2" s="3">
+        <v>167211092.95546621</v>
       </c>
       <c r="U2">
-        <v>94.654737718416001</v>
+        <v>93.791541562997509</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B3">
-        <v>70</v>
-      </c>
-      <c r="C3">
-        <v>9170974.8322425764</v>
+        <v>20</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2811376.23316054</v>
       </c>
       <c r="D3">
-        <v>2.5409999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E3">
         <v>11.942294831374801</v>
@@ -1557,63 +1597,63 @@
         <v>104.5</v>
       </c>
       <c r="G3">
-        <v>118.98329483137481</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H3">
-        <v>1091192802.3558359</v>
-      </c>
-      <c r="I3">
-        <v>102074956.3347913</v>
+        <v>329404159.36887407</v>
+      </c>
+      <c r="I3" s="3">
+        <v>31291232.555957101</v>
       </c>
       <c r="J3">
-        <v>-989117846.02104509</v>
+        <v>-298112926.81291699</v>
       </c>
       <c r="K3">
         <v>200</v>
       </c>
       <c r="L3">
-        <v>45855</v>
+        <v>14057</v>
       </c>
       <c r="M3">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="N3">
-        <v>6419700</v>
+        <v>562280</v>
       </c>
       <c r="O3">
-        <v>1925910</v>
+        <v>168684</v>
       </c>
       <c r="P3">
-        <v>5142179.7</v>
-      </c>
-      <c r="Q3">
-        <v>851066464.43211102</v>
+        <v>450386.28</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>260895714.43729809</v>
       </c>
       <c r="R3">
-        <v>42553323.221605547</v>
-      </c>
-      <c r="S3">
-        <v>47695502.921605557</v>
-      </c>
-      <c r="T3">
-        <v>803370961.51050544</v>
+        <v>13044785.721864911</v>
+      </c>
+      <c r="S3" s="3">
+        <v>13495172.00186491</v>
+      </c>
+      <c r="T3" s="3">
+        <v>247400542.43543321</v>
       </c>
       <c r="U3">
-        <v>94.395795755689733</v>
+        <v>94.827369230279842</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>7053425.2101383004</v>
+        <v>90</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2445593.2885980201</v>
       </c>
       <c r="D4">
-        <v>0.72599999999999998</v>
+        <v>3.2669999999999999</v>
       </c>
       <c r="E4">
         <v>11.942294831374801</v>
@@ -1622,63 +1662,63 @@
         <v>104.5</v>
       </c>
       <c r="G4">
-        <v>117.16829483137479</v>
+        <v>119.70929483137481</v>
       </c>
       <c r="H4">
-        <v>826437804.59253597</v>
-      </c>
-      <c r="I4">
-        <v>78506165.757247716</v>
+        <v>292760248.02241182</v>
+      </c>
+      <c r="I4" s="3">
+        <v>27219988.355944332</v>
       </c>
       <c r="J4">
-        <v>-747931638.83528829</v>
+        <v>-265540259.6664674</v>
       </c>
       <c r="K4">
         <v>200</v>
       </c>
       <c r="L4">
-        <v>35268</v>
+        <v>12228</v>
       </c>
       <c r="M4">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="N4">
-        <v>1410720</v>
+        <v>2201040</v>
       </c>
       <c r="O4">
-        <v>423216</v>
+        <v>660312</v>
       </c>
       <c r="P4">
-        <v>1129986.72</v>
-      </c>
-      <c r="Q4">
-        <v>654557859.50083423</v>
+        <v>1763033.04</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>226951057.18189621</v>
       </c>
       <c r="R4">
-        <v>32727892.97504171</v>
-      </c>
-      <c r="S4">
-        <v>33857879.695041709</v>
-      </c>
-      <c r="T4">
-        <v>620699979.80579257</v>
+        <v>11347552.85909481</v>
+      </c>
+      <c r="S4" s="3">
+        <v>13110585.899094811</v>
+      </c>
+      <c r="T4" s="3">
+        <v>213840471.28280139</v>
       </c>
       <c r="U4">
-        <v>94.827366411754383</v>
+        <v>94.223165971601105</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="B5">
-        <v>40</v>
-      </c>
-      <c r="C5">
-        <v>6878231.1241819309</v>
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>611398.32214950491</v>
       </c>
       <c r="D5">
-        <v>1.452</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E5">
         <v>11.942294831374801</v>
@@ -1687,63 +1727,63 @@
         <v>104.5</v>
       </c>
       <c r="G5">
-        <v>117.89429483137479</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H5">
-        <v>810904208.07264304</v>
-      </c>
-      <c r="I5">
-        <v>76556217.251093432</v>
+        <v>71414561.278080791</v>
+      </c>
+      <c r="I5" s="3">
+        <v>6804997.088986082</v>
       </c>
       <c r="J5">
-        <v>-734347990.82154965</v>
+        <v>-64609564.189094707</v>
       </c>
       <c r="K5">
         <v>200</v>
       </c>
       <c r="L5">
-        <v>34392</v>
+        <v>3057</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N5">
-        <v>2751360</v>
+        <v>61140</v>
       </c>
       <c r="O5">
-        <v>825408</v>
+        <v>18342</v>
       </c>
       <c r="P5">
-        <v>2203839.36</v>
-      </c>
-      <c r="Q5">
-        <v>638299848.32408321</v>
+        <v>48973.14</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>56737764.295474052</v>
       </c>
       <c r="R5">
-        <v>31914992.416204158</v>
-      </c>
-      <c r="S5">
-        <v>34118831.776204161</v>
-      </c>
-      <c r="T5">
-        <v>604181016.5478791</v>
+        <v>2836888.214773702</v>
+      </c>
+      <c r="S5" s="3">
+        <v>2885861.354773703</v>
+      </c>
+      <c r="T5" s="3">
+        <v>53851902.940700352</v>
       </c>
       <c r="U5">
-        <v>94.654732902446028</v>
+        <v>94.913685107955672</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>70</v>
-      </c>
-      <c r="C6">
-        <v>6113983.22149505</v>
+        <v>10</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3518746.2707086438</v>
       </c>
       <c r="D6">
-        <v>2.5409999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E6">
         <v>11.942294831374801</v>
@@ -1752,63 +1792,63 @@
         <v>104.5</v>
       </c>
       <c r="G6">
-        <v>118.98329483137481</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H6">
-        <v>727461868.23722422</v>
-      </c>
-      <c r="I6">
-        <v>68049970.889860839</v>
+        <v>411008195.58692372</v>
+      </c>
+      <c r="I6" s="3">
+        <v>39164415.834294163</v>
       </c>
       <c r="J6">
-        <v>-659411897.34736335</v>
+        <v>-371843779.75262958</v>
       </c>
       <c r="K6">
         <v>200</v>
       </c>
       <c r="L6">
-        <v>30570</v>
+        <v>17594</v>
       </c>
       <c r="M6">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="N6">
-        <v>4279800</v>
+        <v>351880</v>
       </c>
       <c r="O6">
-        <v>1283940</v>
+        <v>105564</v>
       </c>
       <c r="P6">
-        <v>3428119.8</v>
-      </c>
-      <c r="Q6">
-        <v>567377642.95474064</v>
+        <v>281855.88</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>326539653.92176211</v>
       </c>
       <c r="R6">
-        <v>28368882.14773703</v>
-      </c>
-      <c r="S6">
-        <v>31797001.947737031</v>
-      </c>
-      <c r="T6">
-        <v>535580641.00700361</v>
+        <v>16326982.696088109</v>
+      </c>
+      <c r="S6" s="3">
+        <v>16608838.57608811</v>
+      </c>
+      <c r="T6" s="3">
+        <v>309930815.34567398</v>
       </c>
       <c r="U6">
-        <v>94.395795755689747</v>
+        <v>94.913684026850973</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B7">
-        <v>40</v>
-      </c>
-      <c r="C7">
-        <v>5044036.1577334162</v>
+        <v>10</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1222796.64429901</v>
       </c>
       <c r="D7">
-        <v>1.452</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E7">
         <v>11.942294831374801</v>
@@ -1817,63 +1857,63 @@
         <v>104.5</v>
       </c>
       <c r="G7">
-        <v>117.89429483137479</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H7">
-        <v>594663085.91993821</v>
-      </c>
-      <c r="I7">
-        <v>56141225.984135188</v>
+        <v>142829122.55616161</v>
+      </c>
+      <c r="I7" s="3">
+        <v>13609994.17797216</v>
       </c>
       <c r="J7">
-        <v>-538521859.93580306</v>
+        <v>-129219128.3781894</v>
       </c>
       <c r="K7">
         <v>200</v>
       </c>
       <c r="L7">
-        <v>25221</v>
+        <v>6114</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N7">
-        <v>2017680</v>
+        <v>122280</v>
       </c>
       <c r="O7">
-        <v>605304</v>
+        <v>36684</v>
       </c>
       <c r="P7">
-        <v>1616161.68</v>
-      </c>
-      <c r="Q7">
-        <v>468086555.43766099</v>
+        <v>97946.28</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>113475528.5909481</v>
       </c>
       <c r="R7">
-        <v>23404327.771883052</v>
-      </c>
-      <c r="S7">
-        <v>25020489.451883052</v>
-      </c>
-      <c r="T7">
-        <v>443066065.98577797</v>
+        <v>5673776.4295474049</v>
+      </c>
+      <c r="S7" s="3">
+        <v>5771722.7095474051</v>
+      </c>
+      <c r="T7" s="3">
+        <v>107703805.8814007</v>
       </c>
       <c r="U7">
-        <v>94.654730164490871</v>
+        <v>94.913685107955672</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B8">
-        <v>130</v>
-      </c>
-      <c r="C8">
-        <v>5044036.1577334162</v>
+        <v>50</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1530064.6578074801</v>
       </c>
       <c r="D8">
-        <v>4.7189999999999994</v>
+        <v>1.8149999999999999</v>
       </c>
       <c r="E8">
         <v>11.942294831374801</v>
@@ -1882,63 +1922,63 @@
         <v>104.5</v>
       </c>
       <c r="G8">
-        <v>121.1612948313748</v>
+        <v>118.25729483137479</v>
       </c>
       <c r="H8">
-        <v>611141952.04725325</v>
-      </c>
-      <c r="I8">
-        <v>56141225.984135188</v>
+        <v>180941307.34940571</v>
+      </c>
+      <c r="I8" s="3">
+        <v>17029954.393290471</v>
       </c>
       <c r="J8">
-        <v>-555000726.0631181</v>
+        <v>-163911352.95611519</v>
       </c>
       <c r="K8">
         <v>200</v>
       </c>
       <c r="L8">
-        <v>25221</v>
+        <v>7651</v>
       </c>
       <c r="M8">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>6557460</v>
+        <v>765100</v>
       </c>
       <c r="O8">
-        <v>1967238</v>
+        <v>229530</v>
       </c>
       <c r="P8">
-        <v>5252525.46</v>
-      </c>
-      <c r="Q8">
-        <v>468086555.43766099</v>
+        <v>612845.1</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>141990000.24453411</v>
       </c>
       <c r="R8">
-        <v>23404327.771883052</v>
-      </c>
-      <c r="S8">
-        <v>28656853.231883049</v>
-      </c>
-      <c r="T8">
-        <v>439429702.20577788</v>
+        <v>7099500.0122267054</v>
+      </c>
+      <c r="S8" s="3">
+        <v>7712345.1122267041</v>
+      </c>
+      <c r="T8" s="3">
+        <v>134277655.13230741</v>
       </c>
       <c r="U8">
-        <v>93.877873034595311</v>
+        <v>94.568388549232665</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B9">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>5007446.6160084549</v>
+        <v>110</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2751292.449672773</v>
       </c>
       <c r="D9">
-        <v>0.36299999999999999</v>
+        <v>3.9929999999999999</v>
       </c>
       <c r="E9">
         <v>11.942294831374801</v>
@@ -1947,63 +1987,63 @@
         <v>104.5</v>
       </c>
       <c r="G9">
-        <v>116.80529483137479</v>
+        <v>120.4352948313748</v>
       </c>
       <c r="H9">
-        <v>584896278.33523762</v>
-      </c>
-      <c r="I9">
-        <v>55733976.379572473</v>
+        <v>331352717.34367567</v>
+      </c>
+      <c r="I9" s="3">
+        <v>30622486.90043737</v>
       </c>
       <c r="J9">
-        <v>-529162301.95566517</v>
+        <v>-300730230.44323838</v>
       </c>
       <c r="K9">
         <v>200</v>
       </c>
       <c r="L9">
-        <v>25038</v>
+        <v>13757</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="N9">
-        <v>500760</v>
+        <v>3026540</v>
       </c>
       <c r="O9">
-        <v>150228</v>
+        <v>907962</v>
       </c>
       <c r="P9">
-        <v>401108.76</v>
-      </c>
-      <c r="Q9">
-        <v>464691045.96558458</v>
+        <v>2424258.54</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>255319939.3296333</v>
       </c>
       <c r="R9">
-        <v>23234552.29827923</v>
-      </c>
-      <c r="S9">
-        <v>23635661.058279231</v>
-      </c>
-      <c r="T9">
-        <v>441055384.90730542</v>
+        <v>12765996.96648166</v>
+      </c>
+      <c r="S9" s="3">
+        <v>15190255.506481661</v>
+      </c>
+      <c r="T9" s="3">
+        <v>240129683.82315159</v>
       </c>
       <c r="U9">
-        <v>94.91368270090797</v>
+        <v>94.050501677869306</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B10">
-        <v>130</v>
-      </c>
-      <c r="C10">
-        <v>4585487.4161212882</v>
+        <v>100</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1222796.64429901</v>
       </c>
       <c r="D10">
-        <v>4.7189999999999994</v>
+        <v>3.63</v>
       </c>
       <c r="E10">
         <v>11.942294831374801</v>
@@ -2012,63 +2052,63 @@
         <v>104.5</v>
       </c>
       <c r="G10">
-        <v>121.1612948313748</v>
+        <v>120.0722948313748</v>
       </c>
       <c r="H10">
-        <v>555583592.77023041</v>
-      </c>
-      <c r="I10">
-        <v>51037478.167395636</v>
+        <v>146823999.19308639</v>
+      </c>
+      <c r="I10" s="3">
+        <v>13609994.17797216</v>
       </c>
       <c r="J10">
-        <v>-504546114.60283482</v>
+        <v>-133214005.01511431</v>
       </c>
       <c r="K10">
         <v>200</v>
       </c>
       <c r="L10">
-        <v>22928</v>
+        <v>6114</v>
       </c>
       <c r="M10">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="N10">
-        <v>5961280</v>
+        <v>1222800</v>
       </c>
       <c r="O10">
-        <v>1788384</v>
+        <v>366840</v>
       </c>
       <c r="P10">
-        <v>4774985.28</v>
-      </c>
-      <c r="Q10">
-        <v>425533232.21605551</v>
+        <v>979462.79999999993</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>113475528.5909481</v>
       </c>
       <c r="R10">
-        <v>21276661.610802781</v>
-      </c>
-      <c r="S10">
-        <v>26051646.890802778</v>
-      </c>
-      <c r="T10">
-        <v>399481585.32525271</v>
+        <v>5673776.4295474049</v>
+      </c>
+      <c r="S10" s="3">
+        <v>6653239.2295474047</v>
+      </c>
+      <c r="T10" s="3">
+        <v>106822289.36140069</v>
       </c>
       <c r="U10">
-        <v>93.877881932949563</v>
+        <v>94.136851079556791</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B11">
-        <v>130</v>
-      </c>
-      <c r="C11">
-        <v>4585487.4161212882</v>
+        <v>10</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1528495.805373763</v>
       </c>
       <c r="D11">
-        <v>4.7189999999999994</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E11">
         <v>11.942294831374801</v>
@@ -2077,63 +2117,63 @@
         <v>104.5</v>
       </c>
       <c r="G11">
-        <v>121.1612948313748</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H11">
-        <v>555583592.77023041</v>
-      </c>
-      <c r="I11">
-        <v>51037478.167395636</v>
+        <v>178536403.19520199</v>
+      </c>
+      <c r="I11" s="3">
+        <v>17012492.72246521</v>
       </c>
       <c r="J11">
-        <v>-504546114.60283482</v>
+        <v>-161523910.47273681</v>
       </c>
       <c r="K11">
         <v>200</v>
       </c>
       <c r="L11">
-        <v>22928</v>
+        <v>7643</v>
       </c>
       <c r="M11">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="N11">
-        <v>5961280</v>
+        <v>152860</v>
       </c>
       <c r="O11">
-        <v>1788384</v>
+        <v>45858</v>
       </c>
       <c r="P11">
-        <v>4774985.28</v>
-      </c>
-      <c r="Q11">
-        <v>425533232.21605551</v>
+        <v>122440.86</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>141844410.73868519</v>
       </c>
       <c r="R11">
-        <v>21276661.610802781</v>
-      </c>
-      <c r="S11">
-        <v>26051646.890802778</v>
-      </c>
-      <c r="T11">
-        <v>399481585.32525271</v>
+        <v>7092220.5369342566</v>
+      </c>
+      <c r="S11" s="3">
+        <v>7214661.3969342578</v>
+      </c>
+      <c r="T11" s="3">
+        <v>134629749.34175089</v>
       </c>
       <c r="U11">
-        <v>93.877881932949563</v>
+        <v>94.913679460923149</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B12">
-        <v>50</v>
-      </c>
-      <c r="C12">
-        <v>4341226.5003561927</v>
+        <v>20</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1799280.7892227459</v>
       </c>
       <c r="D12">
-        <v>1.8149999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E12">
         <v>11.942294831374801</v>
@@ -2142,63 +2182,63 @@
         <v>104.5</v>
       </c>
       <c r="G12">
-        <v>118.25729483137479</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H12">
-        <v>513381702.18239969</v>
-      </c>
-      <c r="I12">
-        <v>48318800.73483295</v>
+        <v>210818661.99607939</v>
+      </c>
+      <c r="I12" s="3">
+        <v>20026388.83581255</v>
       </c>
       <c r="J12">
-        <v>-465062901.44756669</v>
+        <v>-190792273.16026691</v>
       </c>
       <c r="K12">
         <v>200</v>
       </c>
       <c r="L12">
-        <v>21707</v>
+        <v>8997</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N12">
-        <v>2170700</v>
+        <v>359880</v>
       </c>
       <c r="O12">
-        <v>651210</v>
+        <v>107964</v>
       </c>
       <c r="P12">
-        <v>1738730.7</v>
-      </c>
-      <c r="Q12">
-        <v>402865819.2330547</v>
+        <v>288263.88</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>166973257.23987079</v>
       </c>
       <c r="R12">
-        <v>20143290.96165273</v>
-      </c>
-      <c r="S12">
-        <v>21882021.661652729</v>
-      </c>
-      <c r="T12">
-        <v>380983797.57140201</v>
+        <v>8348662.8619935401</v>
+      </c>
+      <c r="S12" s="3">
+        <v>8636926.7419935409</v>
+      </c>
+      <c r="T12" s="3">
+        <v>158336330.4978773</v>
       </c>
       <c r="U12">
-        <v>94.568409476060779</v>
+        <v>94.827359252155034</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>4263207.4643862695</v>
+        <v>40</v>
+      </c>
+      <c r="C13" s="2">
+        <v>4186288.3354100399</v>
       </c>
       <c r="D13">
-        <v>0.36299999999999999</v>
+        <v>1.452</v>
       </c>
       <c r="E13">
         <v>11.942294831374801</v>
@@ -2207,60 +2247,60 @@
         <v>104.5</v>
       </c>
       <c r="G13">
-        <v>116.80529483137479</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H13">
-        <v>497965204.80495578</v>
-      </c>
-      <c r="I13">
-        <v>47450431.795261323</v>
+        <v>493539511.26397651</v>
+      </c>
+      <c r="I13" s="3">
+        <v>46594305.06117031</v>
       </c>
       <c r="J13">
-        <v>-450514773.00969452</v>
+        <v>-446945206.20280612</v>
       </c>
       <c r="K13">
         <v>200</v>
       </c>
       <c r="L13">
-        <v>21317</v>
+        <v>20932</v>
       </c>
       <c r="M13">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N13">
-        <v>426340</v>
+        <v>1674560</v>
       </c>
       <c r="O13">
-        <v>127902</v>
+        <v>502368</v>
       </c>
       <c r="P13">
-        <v>341498.34</v>
-      </c>
-      <c r="Q13">
-        <v>395625652.69504571</v>
+        <v>1341322.56</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>388487557.5260517</v>
       </c>
       <c r="R13">
-        <v>19781282.634752281</v>
-      </c>
-      <c r="S13">
-        <v>20122780.974752281</v>
-      </c>
-      <c r="T13">
-        <v>375502871.7202934</v>
+        <v>19424377.876302589</v>
+      </c>
+      <c r="S13" s="3">
+        <v>20765700.43630258</v>
+      </c>
+      <c r="T13" s="3">
+        <v>367721857.0897491</v>
       </c>
       <c r="U13">
-        <v>94.913681446672214</v>
+        <v>94.654732169920237</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>30</v>
       </c>
-      <c r="C14">
-        <v>4186288.3354100399</v>
+      <c r="C14" s="2">
+        <v>1929224.578184532</v>
       </c>
       <c r="D14">
         <v>1.089</v>
@@ -2275,60 +2315,60 @@
         <v>117.53129483137479</v>
       </c>
       <c r="H14">
-        <v>492019888.59822261</v>
-      </c>
-      <c r="I14">
-        <v>46594305.06117031</v>
+        <v>226744262.69454089</v>
+      </c>
+      <c r="I14" s="3">
+        <v>21472691.636428591</v>
       </c>
       <c r="J14">
-        <v>-445425583.53705227</v>
+        <v>-205271571.05811229</v>
       </c>
       <c r="K14">
         <v>200</v>
       </c>
       <c r="L14">
-        <v>20932</v>
+        <v>9647</v>
       </c>
       <c r="M14">
         <v>60</v>
       </c>
       <c r="N14">
-        <v>1255920</v>
+        <v>578820</v>
       </c>
       <c r="O14">
-        <v>376776</v>
+        <v>173646</v>
       </c>
       <c r="P14">
-        <v>1005991.92</v>
-      </c>
-      <c r="Q14">
-        <v>388487557.5260517</v>
+        <v>463634.82</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>179032040.8555246</v>
       </c>
       <c r="R14">
-        <v>19424377.876302589</v>
-      </c>
-      <c r="S14">
-        <v>20430369.796302591</v>
-      </c>
-      <c r="T14">
-        <v>368057187.72974908</v>
+        <v>8951602.0427762289</v>
+      </c>
+      <c r="S14" s="3">
+        <v>9415236.8627762292</v>
+      </c>
+      <c r="T14" s="3">
+        <v>169616803.99274841</v>
       </c>
       <c r="U14">
-        <v>94.741049127440178</v>
+        <v>94.741032489053651</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B15">
-        <v>40</v>
-      </c>
-      <c r="C15">
-        <v>4186288.3354100399</v>
+        <v>60</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2232687.1122186878</v>
       </c>
       <c r="D15">
-        <v>1.452</v>
+        <v>2.1779999999999999</v>
       </c>
       <c r="E15">
         <v>11.942294831374801</v>
@@ -2337,63 +2377,63 @@
         <v>104.5</v>
       </c>
       <c r="G15">
-        <v>117.89429483137479</v>
+        <v>118.62029483137481</v>
       </c>
       <c r="H15">
-        <v>493539511.26397651</v>
-      </c>
-      <c r="I15">
-        <v>46594305.06117031</v>
+        <v>264842003.51759151</v>
+      </c>
+      <c r="I15" s="3">
+        <v>24850296.03262417</v>
       </c>
       <c r="J15">
-        <v>-446945206.20280612</v>
+        <v>-239991707.48496741</v>
       </c>
       <c r="K15">
         <v>200</v>
       </c>
       <c r="L15">
-        <v>20932</v>
+        <v>11164</v>
       </c>
       <c r="M15">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="N15">
-        <v>1674560</v>
+        <v>1339680</v>
       </c>
       <c r="O15">
-        <v>502368</v>
+        <v>401904</v>
       </c>
       <c r="P15">
-        <v>1341322.56</v>
-      </c>
-      <c r="Q15">
-        <v>388487557.5260517</v>
+        <v>1073083.68</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>207193364.0138942</v>
       </c>
       <c r="R15">
-        <v>19424377.876302589</v>
-      </c>
-      <c r="S15">
-        <v>20765700.43630258</v>
-      </c>
-      <c r="T15">
-        <v>367721857.0897491</v>
+        <v>10359668.20069471</v>
+      </c>
+      <c r="S15" s="3">
+        <v>11432751.88069471</v>
+      </c>
+      <c r="T15" s="3">
+        <v>195760612.13319951</v>
       </c>
       <c r="U15">
-        <v>94.654732169920237</v>
+        <v>94.482085883827793</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>10</v>
-      </c>
-      <c r="C16">
-        <v>3518746.2707086438</v>
+        <v>70</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2200588.37873897</v>
       </c>
       <c r="D16">
-        <v>0.36299999999999999</v>
+        <v>2.5409999999999999</v>
       </c>
       <c r="E16">
         <v>11.942294831374801</v>
@@ -2402,63 +2442,63 @@
         <v>104.5</v>
       </c>
       <c r="G16">
-        <v>116.80529483137479</v>
+        <v>118.98329483137481</v>
       </c>
       <c r="H16">
-        <v>411008195.58692372</v>
-      </c>
-      <c r="I16">
-        <v>39164415.834294163</v>
+        <v>261833255.86999589</v>
+      </c>
+      <c r="I16" s="3">
+        <v>24493030.106342789</v>
       </c>
       <c r="J16">
-        <v>-371843779.75262958</v>
+        <v>-237340225.7636531</v>
       </c>
       <c r="K16">
         <v>200</v>
       </c>
       <c r="L16">
-        <v>17594</v>
+        <v>11003</v>
       </c>
       <c r="M16">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="N16">
-        <v>351880</v>
+        <v>1540420</v>
       </c>
       <c r="O16">
-        <v>105564</v>
+        <v>462126</v>
       </c>
       <c r="P16">
-        <v>281855.88</v>
-      </c>
-      <c r="Q16">
-        <v>326539653.92176211</v>
+        <v>1233876.42</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>204214601.54697639</v>
       </c>
       <c r="R16">
-        <v>16326982.696088109</v>
-      </c>
-      <c r="S16">
-        <v>16608838.57608811</v>
-      </c>
-      <c r="T16">
-        <v>309930815.34567398</v>
+        <v>10210730.077348821</v>
+      </c>
+      <c r="S16" s="3">
+        <v>11444606.497348821</v>
+      </c>
+      <c r="T16" s="3">
+        <v>192769995.0496276</v>
       </c>
       <c r="U16">
-        <v>94.913684026850973</v>
+        <v>94.395794223011933</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B17">
-        <v>70</v>
-      </c>
-      <c r="C17">
-        <v>3201858.8671254199</v>
+        <v>10</v>
+      </c>
+      <c r="C17" s="2">
+        <v>625251.12010516541</v>
       </c>
       <c r="D17">
-        <v>2.5409999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E17">
         <v>11.942294831374801</v>
@@ -2467,63 +2507,63 @@
         <v>104.5</v>
       </c>
       <c r="G17">
-        <v>118.98329483137481</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H17">
-        <v>380967717.59563547</v>
-      </c>
-      <c r="I17">
-        <v>35637389.70288635</v>
+        <v>73032641.427531183</v>
+      </c>
+      <c r="I17" s="3">
+        <v>6959181.7609870806</v>
       </c>
       <c r="J17">
-        <v>-345330327.89274919</v>
+        <v>-66073459.666544102</v>
       </c>
       <c r="K17">
         <v>200</v>
       </c>
       <c r="L17">
-        <v>16010</v>
+        <v>3127</v>
       </c>
       <c r="M17">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="N17">
-        <v>2241400</v>
+        <v>62540</v>
       </c>
       <c r="O17">
-        <v>672420</v>
+        <v>18762</v>
       </c>
       <c r="P17">
-        <v>1795361.4</v>
-      </c>
-      <c r="Q17">
-        <v>297132502.86923897</v>
+        <v>50094.54</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>58023303.945759349</v>
       </c>
       <c r="R17">
-        <v>14856625.14346195</v>
-      </c>
-      <c r="S17">
-        <v>16651986.54346195</v>
-      </c>
-      <c r="T17">
-        <v>280480516.32577711</v>
+        <v>2901165.197287967</v>
+      </c>
+      <c r="S17" s="3">
+        <v>2951259.737287967</v>
+      </c>
+      <c r="T17" s="3">
+        <v>55072044.20847138</v>
       </c>
       <c r="U17">
-        <v>94.395770781498769</v>
+        <v>94.913664792258601</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B18">
-        <v>20</v>
-      </c>
-      <c r="C18">
-        <v>3148741.381139806</v>
+        <v>10</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1421069.1547954229</v>
       </c>
       <c r="D18">
-        <v>0.72599999999999998</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E18">
         <v>11.942294831374801</v>
@@ -2532,63 +2572,63 @@
         <v>104.5</v>
       </c>
       <c r="G18">
-        <v>117.16829483137479</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H18">
-        <v>368932658.49313903</v>
-      </c>
-      <c r="I18">
-        <v>35046180.462671958</v>
+        <v>165988401.60165191</v>
+      </c>
+      <c r="I18" s="3">
+        <v>15816810.598420439</v>
       </c>
       <c r="J18">
-        <v>-333886478.03046709</v>
+        <v>-150171591.0032315</v>
       </c>
       <c r="K18">
         <v>200</v>
       </c>
       <c r="L18">
-        <v>15744</v>
+        <v>7106</v>
       </c>
       <c r="M18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N18">
-        <v>629760</v>
+        <v>142120</v>
       </c>
       <c r="O18">
-        <v>188928</v>
+        <v>42636</v>
       </c>
       <c r="P18">
-        <v>504437.76000000001</v>
-      </c>
-      <c r="Q18">
-        <v>292203200.16977388</v>
+        <v>113838.12</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>131875217.5650152</v>
       </c>
       <c r="R18">
-        <v>14610160.0084887</v>
-      </c>
-      <c r="S18">
-        <v>15114597.7684887</v>
-      </c>
-      <c r="T18">
-        <v>277088602.40128517</v>
+        <v>6593760.878250761</v>
+      </c>
+      <c r="S18" s="3">
+        <v>6707598.9982507611</v>
+      </c>
+      <c r="T18" s="3">
+        <v>125167618.5667645</v>
       </c>
       <c r="U18">
-        <v>94.827367475884273</v>
+        <v>94.913677397389776</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B19">
-        <v>50</v>
-      </c>
-      <c r="C19">
-        <v>2886986.9764777748</v>
+        <v>40</v>
+      </c>
+      <c r="C19" s="2">
+        <v>5044036.1577334162</v>
       </c>
       <c r="D19">
-        <v>1.8149999999999999</v>
+        <v>1.452</v>
       </c>
       <c r="E19">
         <v>11.942294831374801</v>
@@ -2597,63 +2637,63 @@
         <v>104.5</v>
       </c>
       <c r="G19">
-        <v>118.25729483137479</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H19">
-        <v>341407270.05167162</v>
-      </c>
-      <c r="I19">
-        <v>32132796.671411179</v>
+        <v>594663085.91993821</v>
+      </c>
+      <c r="I19" s="3">
+        <v>56141225.984135188</v>
       </c>
       <c r="J19">
-        <v>-309274473.38026041</v>
+        <v>-538521859.93580306</v>
       </c>
       <c r="K19">
         <v>200</v>
       </c>
       <c r="L19">
-        <v>14435</v>
+        <v>25221</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N19">
-        <v>1443500</v>
+        <v>2017680</v>
       </c>
       <c r="O19">
-        <v>433050</v>
+        <v>605304</v>
       </c>
       <c r="P19">
-        <v>1156243.5</v>
-      </c>
-      <c r="Q19">
-        <v>267912391.4171375</v>
+        <v>1616161.68</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>468086555.43766099</v>
       </c>
       <c r="R19">
-        <v>13395619.57085688</v>
-      </c>
-      <c r="S19">
-        <v>14551863.07085688</v>
-      </c>
-      <c r="T19">
-        <v>253360528.34628069</v>
+        <v>23404327.771883052</v>
+      </c>
+      <c r="S19" s="3">
+        <v>25020489.451883052</v>
+      </c>
+      <c r="T19" s="3">
+        <v>443066065.98577797</v>
       </c>
       <c r="U19">
-        <v>94.568424777262464</v>
+        <v>94.654730164490871</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B20">
-        <v>20</v>
-      </c>
-      <c r="C20">
-        <v>2811376.23316054</v>
+        <v>130</v>
+      </c>
+      <c r="C20" s="2">
+        <v>4585487.4161212882</v>
       </c>
       <c r="D20">
-        <v>0.72599999999999998</v>
+        <v>4.7189999999999994</v>
       </c>
       <c r="E20">
         <v>11.942294831374801</v>
@@ -2662,63 +2702,63 @@
         <v>104.5</v>
       </c>
       <c r="G20">
-        <v>117.16829483137479</v>
+        <v>121.1612948313748</v>
       </c>
       <c r="H20">
-        <v>329404159.36887407</v>
-      </c>
-      <c r="I20">
-        <v>31291232.555957101</v>
+        <v>555583592.77023041</v>
+      </c>
+      <c r="I20" s="3">
+        <v>51037478.167395636</v>
       </c>
       <c r="J20">
-        <v>-298112926.81291699</v>
+        <v>-504546114.60283482</v>
       </c>
       <c r="K20">
         <v>200</v>
       </c>
       <c r="L20">
-        <v>14057</v>
+        <v>22928</v>
       </c>
       <c r="M20">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="N20">
-        <v>562280</v>
+        <v>5961280</v>
       </c>
       <c r="O20">
-        <v>168684</v>
+        <v>1788384</v>
       </c>
       <c r="P20">
-        <v>450386.28</v>
-      </c>
-      <c r="Q20">
-        <v>260895714.43729809</v>
+        <v>4774985.28</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>425533232.21605551</v>
       </c>
       <c r="R20">
-        <v>13044785.721864911</v>
-      </c>
-      <c r="S20">
-        <v>13495172.00186491</v>
-      </c>
-      <c r="T20">
-        <v>247400542.43543321</v>
+        <v>21276661.610802781</v>
+      </c>
+      <c r="S20" s="3">
+        <v>26051646.890802778</v>
+      </c>
+      <c r="T20" s="3">
+        <v>399481585.32525271</v>
       </c>
       <c r="U20">
-        <v>94.827369230279842</v>
+        <v>93.877881932949563</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B21">
-        <v>170</v>
-      </c>
-      <c r="C21">
-        <v>2763338.5303054149</v>
+        <v>10</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1057686.228970353</v>
       </c>
       <c r="D21">
-        <v>6.1709999999999994</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E21">
         <v>11.942294831374801</v>
@@ -2727,63 +2767,63 @@
         <v>104.5</v>
       </c>
       <c r="G21">
-        <v>122.6132948313748</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H21">
-        <v>338822041.93523568</v>
-      </c>
-      <c r="I21">
-        <v>30756562.41335443</v>
+        <v>123543351.813967</v>
+      </c>
+      <c r="I21" s="3">
+        <v>11772279.132038411</v>
       </c>
       <c r="J21">
-        <v>-308065479.52188128</v>
+        <v>-111771072.6819286</v>
       </c>
       <c r="K21">
         <v>200</v>
       </c>
       <c r="L21">
-        <v>13817</v>
+        <v>5289</v>
       </c>
       <c r="M21">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="N21">
-        <v>4697780</v>
+        <v>105780</v>
       </c>
       <c r="O21">
-        <v>1409334</v>
+        <v>31734</v>
       </c>
       <c r="P21">
-        <v>3762921.78</v>
-      </c>
-      <c r="Q21">
-        <v>256437815.61234251</v>
+        <v>84729.78</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>98153282.048448712</v>
       </c>
       <c r="R21">
-        <v>12821890.78061712</v>
-      </c>
-      <c r="S21">
-        <v>16584812.560617119</v>
-      </c>
-      <c r="T21">
-        <v>239853003.05172539</v>
+        <v>4907664.1024224358</v>
+      </c>
+      <c r="S21" s="3">
+        <v>4992393.882422436</v>
+      </c>
+      <c r="T21" s="3">
+        <v>93160888.166026279</v>
       </c>
       <c r="U21">
-        <v>93.532618221296815</v>
+        <v>94.913676060309257</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B22">
-        <v>110</v>
-      </c>
-      <c r="C22">
-        <v>2751292.449672773</v>
+        <v>20</v>
+      </c>
+      <c r="C22" s="2">
+        <v>7053425.2101383004</v>
       </c>
       <c r="D22">
-        <v>3.9929999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E22">
         <v>11.942294831374801</v>
@@ -2792,63 +2832,63 @@
         <v>104.5</v>
       </c>
       <c r="G22">
-        <v>120.4352948313748</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H22">
-        <v>331352717.34367567</v>
-      </c>
-      <c r="I22">
-        <v>30622486.90043737</v>
+        <v>826437804.59253597</v>
+      </c>
+      <c r="I22" s="3">
+        <v>78506165.757247716</v>
       </c>
       <c r="J22">
-        <v>-300730230.44323838</v>
+        <v>-747931638.83528829</v>
       </c>
       <c r="K22">
         <v>200</v>
       </c>
       <c r="L22">
-        <v>13757</v>
+        <v>35268</v>
       </c>
       <c r="M22">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="N22">
-        <v>3026540</v>
+        <v>1410720</v>
       </c>
       <c r="O22">
-        <v>907962</v>
+        <v>423216</v>
       </c>
       <c r="P22">
-        <v>2424258.54</v>
-      </c>
-      <c r="Q22">
-        <v>255319939.3296333</v>
+        <v>1129986.72</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>654557859.50083423</v>
       </c>
       <c r="R22">
-        <v>12765996.96648166</v>
-      </c>
-      <c r="S22">
-        <v>15190255.506481661</v>
-      </c>
-      <c r="T22">
-        <v>240129683.82315159</v>
+        <v>32727892.97504171</v>
+      </c>
+      <c r="S22" s="3">
+        <v>33857879.695041709</v>
+      </c>
+      <c r="T22" s="3">
+        <v>620699979.80579257</v>
       </c>
       <c r="U22">
-        <v>94.050501677869306</v>
+        <v>94.827366411754383</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B23">
-        <v>110</v>
-      </c>
-      <c r="C23">
-        <v>2445593.2885980201</v>
+        <v>70</v>
+      </c>
+      <c r="C23" s="2">
+        <v>9170974.8322425764</v>
       </c>
       <c r="D23">
-        <v>3.9929999999999999</v>
+        <v>2.5409999999999999</v>
       </c>
       <c r="E23">
         <v>11.942294831374801</v>
@@ -2857,63 +2897,63 @@
         <v>104.5</v>
       </c>
       <c r="G23">
-        <v>120.4352948313748</v>
+        <v>118.98329483137481</v>
       </c>
       <c r="H23">
-        <v>294535748.74993402</v>
-      </c>
-      <c r="I23">
-        <v>27219988.355944332</v>
+        <v>1091192802.3558359</v>
+      </c>
+      <c r="I23" s="3">
+        <v>102074956.3347913</v>
       </c>
       <c r="J23">
-        <v>-267315760.39398959</v>
+        <v>-989117846.02104509</v>
       </c>
       <c r="K23">
         <v>200</v>
       </c>
       <c r="L23">
-        <v>12228</v>
+        <v>45855</v>
       </c>
       <c r="M23">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="N23">
-        <v>2690160</v>
+        <v>6419700</v>
       </c>
       <c r="O23">
-        <v>807048</v>
+        <v>1925910</v>
       </c>
       <c r="P23">
-        <v>2154818.16</v>
-      </c>
-      <c r="Q23">
-        <v>226951057.18189621</v>
+        <v>5142179.7</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>851066464.43211102</v>
       </c>
       <c r="R23">
-        <v>11347552.85909481</v>
-      </c>
-      <c r="S23">
-        <v>13502371.01909481</v>
-      </c>
-      <c r="T23">
-        <v>213448686.16280141</v>
+        <v>42553323.221605547</v>
+      </c>
+      <c r="S23" s="3">
+        <v>47695502.921605557</v>
+      </c>
+      <c r="T23" s="3">
+        <v>803370961.51050544</v>
       </c>
       <c r="U23">
-        <v>94.050536187512463</v>
+        <v>94.395795755689733</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B24">
-        <v>90</v>
-      </c>
-      <c r="C24">
-        <v>2445593.2885980201</v>
+        <v>20</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3148741.381139806</v>
       </c>
       <c r="D24">
-        <v>3.2669999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E24">
         <v>11.942294831374801</v>
@@ -2922,63 +2962,63 @@
         <v>104.5</v>
       </c>
       <c r="G24">
-        <v>119.70929483137481</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H24">
-        <v>292760248.02241182</v>
-      </c>
-      <c r="I24">
-        <v>27219988.355944332</v>
+        <v>368932658.49313903</v>
+      </c>
+      <c r="I24" s="3">
+        <v>35046180.462671958</v>
       </c>
       <c r="J24">
-        <v>-265540259.6664674</v>
+        <v>-333886478.03046709</v>
       </c>
       <c r="K24">
         <v>200</v>
       </c>
       <c r="L24">
-        <v>12228</v>
+        <v>15744</v>
       </c>
       <c r="M24">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="N24">
-        <v>2201040</v>
+        <v>629760</v>
       </c>
       <c r="O24">
-        <v>660312</v>
+        <v>188928</v>
       </c>
       <c r="P24">
-        <v>1763033.04</v>
-      </c>
-      <c r="Q24">
-        <v>226951057.18189621</v>
+        <v>504437.76000000001</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>292203200.16977388</v>
       </c>
       <c r="R24">
-        <v>11347552.85909481</v>
-      </c>
-      <c r="S24">
-        <v>13110585.899094811</v>
-      </c>
-      <c r="T24">
-        <v>213840471.28280139</v>
+        <v>14610160.0084887</v>
+      </c>
+      <c r="S24" s="3">
+        <v>15114597.7684887</v>
+      </c>
+      <c r="T24" s="3">
+        <v>277088602.40128517</v>
       </c>
       <c r="U24">
-        <v>94.223165971601105</v>
+        <v>94.827367475884273</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25">
-        <v>60</v>
-      </c>
-      <c r="C25">
-        <v>2232687.1122186878</v>
+        <v>110</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2445593.2885980201</v>
       </c>
       <c r="D25">
-        <v>2.1779999999999999</v>
+        <v>3.9929999999999999</v>
       </c>
       <c r="E25">
         <v>11.942294831374801</v>
@@ -2987,63 +3027,63 @@
         <v>104.5</v>
       </c>
       <c r="G25">
-        <v>118.62029483137481</v>
+        <v>120.4352948313748</v>
       </c>
       <c r="H25">
-        <v>264842003.51759151</v>
-      </c>
-      <c r="I25">
-        <v>24850296.03262417</v>
+        <v>294535748.74993402</v>
+      </c>
+      <c r="I25" s="3">
+        <v>27219988.355944332</v>
       </c>
       <c r="J25">
-        <v>-239991707.48496741</v>
+        <v>-267315760.39398959</v>
       </c>
       <c r="K25">
         <v>200</v>
       </c>
       <c r="L25">
-        <v>11164</v>
+        <v>12228</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="N25">
-        <v>1339680</v>
+        <v>2690160</v>
       </c>
       <c r="O25">
-        <v>401904</v>
+        <v>807048</v>
       </c>
       <c r="P25">
-        <v>1073083.68</v>
-      </c>
-      <c r="Q25">
-        <v>207193364.0138942</v>
+        <v>2154818.16</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>226951057.18189621</v>
       </c>
       <c r="R25">
-        <v>10359668.20069471</v>
-      </c>
-      <c r="S25">
-        <v>11432751.88069471</v>
-      </c>
-      <c r="T25">
-        <v>195760612.13319951</v>
+        <v>11347552.85909481</v>
+      </c>
+      <c r="S25" s="3">
+        <v>13502371.01909481</v>
+      </c>
+      <c r="T25" s="3">
+        <v>213448686.16280141</v>
       </c>
       <c r="U25">
-        <v>94.482085883827793</v>
+        <v>94.050536187512463</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B26">
-        <v>80</v>
-      </c>
-      <c r="C26">
-        <v>2204600.0579179772</v>
+        <v>130</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4585487.4161212882</v>
       </c>
       <c r="D26">
-        <v>2.9039999999999999</v>
+        <v>4.7189999999999994</v>
       </c>
       <c r="E26">
         <v>11.942294831374801</v>
@@ -3052,63 +3092,63 @@
         <v>104.5</v>
       </c>
       <c r="G26">
-        <v>119.34629483137481</v>
+        <v>121.1612948313748</v>
       </c>
       <c r="H26">
-        <v>263110848.49754491</v>
-      </c>
-      <c r="I26">
-        <v>24537680.97329171</v>
+        <v>555583592.77023041</v>
+      </c>
+      <c r="I26" s="3">
+        <v>51037478.167395636</v>
       </c>
       <c r="J26">
-        <v>-238573167.5242531</v>
+        <v>-504546114.60283482</v>
       </c>
       <c r="K26">
         <v>200</v>
       </c>
       <c r="L26">
-        <v>11024</v>
+        <v>22928</v>
       </c>
       <c r="M26">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="N26">
-        <v>1763840</v>
+        <v>5961280</v>
       </c>
       <c r="O26">
-        <v>529152</v>
+        <v>1788384</v>
       </c>
       <c r="P26">
-        <v>1412835.84</v>
-      </c>
-      <c r="Q26">
-        <v>204586885.37478831</v>
+        <v>4774985.28</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>425533232.21605551</v>
       </c>
       <c r="R26">
-        <v>10229344.26873941</v>
-      </c>
-      <c r="S26">
-        <v>11642180.10873941</v>
-      </c>
-      <c r="T26">
-        <v>192944705.26604891</v>
+        <v>21276661.610802781</v>
+      </c>
+      <c r="S26" s="3">
+        <v>26051646.890802778</v>
+      </c>
+      <c r="T26" s="3">
+        <v>399481585.32525271</v>
       </c>
       <c r="U26">
-        <v>94.309420133450018</v>
+        <v>93.877881932949563</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B27">
-        <v>70</v>
-      </c>
-      <c r="C27">
-        <v>2200588.37873897</v>
+        <v>130</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5044036.1577334162</v>
       </c>
       <c r="D27">
-        <v>2.5409999999999999</v>
+        <v>4.7189999999999994</v>
       </c>
       <c r="E27">
         <v>11.942294831374801</v>
@@ -3117,63 +3157,63 @@
         <v>104.5</v>
       </c>
       <c r="G27">
-        <v>118.98329483137481</v>
+        <v>121.1612948313748</v>
       </c>
       <c r="H27">
-        <v>261833255.86999589</v>
-      </c>
-      <c r="I27">
-        <v>24493030.106342789</v>
+        <v>611141952.04725325</v>
+      </c>
+      <c r="I27" s="3">
+        <v>56141225.984135188</v>
       </c>
       <c r="J27">
-        <v>-237340225.7636531</v>
+        <v>-555000726.0631181</v>
       </c>
       <c r="K27">
         <v>200</v>
       </c>
       <c r="L27">
-        <v>11003</v>
+        <v>25221</v>
       </c>
       <c r="M27">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="N27">
-        <v>1540420</v>
+        <v>6557460</v>
       </c>
       <c r="O27">
-        <v>462126</v>
+        <v>1967238</v>
       </c>
       <c r="P27">
-        <v>1233876.42</v>
-      </c>
-      <c r="Q27">
-        <v>204214601.54697639</v>
+        <v>5252525.46</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>468086555.43766099</v>
       </c>
       <c r="R27">
-        <v>10210730.077348821</v>
-      </c>
-      <c r="S27">
-        <v>11444606.497348821</v>
-      </c>
-      <c r="T27">
-        <v>192769995.0496276</v>
+        <v>23404327.771883052</v>
+      </c>
+      <c r="S27" s="3">
+        <v>28656853.231883049</v>
+      </c>
+      <c r="T27" s="3">
+        <v>439429702.20577788</v>
       </c>
       <c r="U27">
-        <v>94.395794223011933</v>
+        <v>93.877873034595311</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B28">
-        <v>40</v>
-      </c>
-      <c r="C28">
-        <v>2077070.866189966</v>
+        <v>170</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2763338.5303054149</v>
       </c>
       <c r="D28">
-        <v>1.452</v>
+        <v>6.1709999999999994</v>
       </c>
       <c r="E28">
         <v>11.942294831374801</v>
@@ -3182,63 +3222,63 @@
         <v>104.5</v>
       </c>
       <c r="G28">
-        <v>117.89429483137479</v>
+        <v>122.6132948313748</v>
       </c>
       <c r="H28">
-        <v>244874805.08425891</v>
-      </c>
-      <c r="I28">
-        <v>23118253.168160029</v>
+        <v>338822041.93523568</v>
+      </c>
+      <c r="I28" s="3">
+        <v>30756562.41335443</v>
       </c>
       <c r="J28">
-        <v>-221756551.9160988</v>
+        <v>-308065479.52188128</v>
       </c>
       <c r="K28">
         <v>200</v>
       </c>
       <c r="L28">
-        <v>10386</v>
+        <v>13817</v>
       </c>
       <c r="M28">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="N28">
-        <v>830880</v>
+        <v>4697780</v>
       </c>
       <c r="O28">
-        <v>249264</v>
+        <v>1409334</v>
       </c>
       <c r="P28">
-        <v>665534.88</v>
-      </c>
-      <c r="Q28">
-        <v>192752176.3824288</v>
+        <v>3762921.78</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>256437815.61234251</v>
       </c>
       <c r="R28">
-        <v>9637608.8191214409</v>
-      </c>
-      <c r="S28">
-        <v>10303143.69912144</v>
-      </c>
-      <c r="T28">
-        <v>182449032.68330741</v>
+        <v>12821890.78061712</v>
+      </c>
+      <c r="S28" s="3">
+        <v>16584812.560617119</v>
+      </c>
+      <c r="T28" s="3">
+        <v>239853003.05172539</v>
       </c>
       <c r="U28">
-        <v>94.654719914197202</v>
+        <v>93.532618221296815</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B29">
-        <v>10</v>
-      </c>
-      <c r="C29">
-        <v>2009816.3726160021</v>
+        <v>60</v>
+      </c>
+      <c r="C29" s="2">
+        <v>837257.66708200797</v>
       </c>
       <c r="D29">
-        <v>0.36299999999999999</v>
+        <v>2.1779999999999999</v>
       </c>
       <c r="E29">
         <v>11.942294831374801</v>
@@ -3247,63 +3287,63 @@
         <v>104.5</v>
       </c>
       <c r="G29">
-        <v>116.80529483137479</v>
+        <v>118.62029483137481</v>
       </c>
       <c r="H29">
-        <v>234757193.9603363</v>
-      </c>
-      <c r="I29">
-        <v>22369695.940552611</v>
+        <v>99315751.319096833</v>
+      </c>
+      <c r="I29" s="3">
+        <v>9318861.012234062</v>
       </c>
       <c r="J29">
-        <v>-212387498.01978371</v>
+        <v>-89996890.306862772</v>
       </c>
       <c r="K29">
         <v>200</v>
       </c>
       <c r="L29">
-        <v>10050</v>
+        <v>4187</v>
       </c>
       <c r="M29">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="N29">
-        <v>201000</v>
+        <v>502440</v>
       </c>
       <c r="O29">
-        <v>60300</v>
+        <v>150732</v>
       </c>
       <c r="P29">
-        <v>161001</v>
-      </c>
-      <c r="Q29">
-        <v>186510959.37876499</v>
+        <v>402454.44</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>77697511.50521034</v>
       </c>
       <c r="R29">
-        <v>9325547.9689382482</v>
-      </c>
-      <c r="S29">
-        <v>9486548.9689382482</v>
-      </c>
-      <c r="T29">
-        <v>177024410.4098267</v>
+        <v>3884875.5752605172</v>
+      </c>
+      <c r="S29" s="3">
+        <v>4287330.0152605167</v>
+      </c>
+      <c r="T29" s="3">
+        <v>73410181.489949822</v>
       </c>
       <c r="U29">
-        <v>94.913677458667166</v>
+        <v>94.482024028564908</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>30</v>
-      </c>
-      <c r="C30">
-        <v>1973284.772889178</v>
+        <v>20</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1052418.5455408951</v>
       </c>
       <c r="D30">
-        <v>1.089</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E30">
         <v>11.942294831374801</v>
@@ -3312,63 +3352,63 @@
         <v>104.5</v>
       </c>
       <c r="G30">
-        <v>117.53129483137479</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H30">
-        <v>231922714.42870039</v>
-      </c>
-      <c r="I30">
-        <v>21963091.243105881</v>
+        <v>123310086.42994221</v>
+      </c>
+      <c r="I30" s="3">
+        <v>11713648.662989801</v>
       </c>
       <c r="J30">
-        <v>-209959623.1855945</v>
+        <v>-111596437.7669524</v>
       </c>
       <c r="K30">
         <v>200</v>
       </c>
       <c r="L30">
-        <v>9867</v>
+        <v>5263</v>
       </c>
       <c r="M30">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="N30">
-        <v>592020</v>
+        <v>210520</v>
       </c>
       <c r="O30">
-        <v>177606</v>
+        <v>63156</v>
       </c>
       <c r="P30">
-        <v>474208.02</v>
-      </c>
-      <c r="Q30">
-        <v>183120826.92411569</v>
+        <v>168626.52</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>97664441.026195064</v>
       </c>
       <c r="R30">
-        <v>9156041.346205784</v>
-      </c>
-      <c r="S30">
-        <v>9630249.3662057836</v>
-      </c>
-      <c r="T30">
-        <v>173490577.55790991</v>
+        <v>4883222.0513097532</v>
+      </c>
+      <c r="S30" s="3">
+        <v>5051848.5713097528</v>
+      </c>
+      <c r="T30" s="3">
+        <v>92612592.454885304</v>
       </c>
       <c r="U30">
-        <v>94.741040913824335</v>
+        <v>94.827340925491228</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B31">
-        <v>30</v>
-      </c>
-      <c r="C31">
-        <v>1929224.578184532</v>
+        <v>10</v>
+      </c>
+      <c r="C31" s="2">
+        <v>588996.33817545942</v>
       </c>
       <c r="D31">
-        <v>1.089</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E31">
         <v>11.942294831374801</v>
@@ -3377,63 +3417,63 @@
         <v>104.5</v>
       </c>
       <c r="G31">
-        <v>117.53129483137479</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H31">
-        <v>226744262.69454089</v>
-      </c>
-      <c r="I31">
-        <v>21472691.636428591</v>
+        <v>68797890.935184672</v>
+      </c>
+      <c r="I31" s="3">
+        <v>6555658.1061852509</v>
       </c>
       <c r="J31">
-        <v>-205271571.05811229</v>
+        <v>-62242232.828999422</v>
       </c>
       <c r="K31">
         <v>200</v>
       </c>
       <c r="L31">
-        <v>9647</v>
+        <v>2945</v>
       </c>
       <c r="M31">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="N31">
-        <v>578820</v>
+        <v>58900</v>
       </c>
       <c r="O31">
-        <v>173646</v>
+        <v>17670</v>
       </c>
       <c r="P31">
-        <v>463634.82</v>
-      </c>
-      <c r="Q31">
-        <v>179032040.8555246</v>
+        <v>47178.9</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>54658860.182682633</v>
       </c>
       <c r="R31">
-        <v>8951602.0427762289</v>
-      </c>
-      <c r="S31">
-        <v>9415236.8627762292</v>
-      </c>
-      <c r="T31">
-        <v>169616803.99274841</v>
+        <v>2732943.009134131</v>
+      </c>
+      <c r="S31" s="3">
+        <v>2780121.9091341309</v>
+      </c>
+      <c r="T31" s="3">
+        <v>51878738.273548499</v>
       </c>
       <c r="U31">
-        <v>94.741032489053651</v>
+        <v>94.913684808204337</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B32">
-        <v>140</v>
-      </c>
-      <c r="C32">
-        <v>1921115.320275252</v>
+        <v>40</v>
+      </c>
+      <c r="C32" s="2">
+        <v>834411.47908190091</v>
       </c>
       <c r="D32">
-        <v>5.0819999999999999</v>
+        <v>1.452</v>
       </c>
       <c r="E32">
         <v>11.942294831374801</v>
@@ -3442,63 +3482,63 @@
         <v>104.5</v>
       </c>
       <c r="G32">
-        <v>121.5242948313748</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H32">
-        <v>233462184.58620071</v>
-      </c>
-      <c r="I32">
-        <v>21382433.82173181</v>
+        <v>98372352.925565153</v>
+      </c>
+      <c r="I32" s="3">
+        <v>9287182.3170957733</v>
       </c>
       <c r="J32">
-        <v>-212079750.76446891</v>
+        <v>-89085170.608469382</v>
       </c>
       <c r="K32">
         <v>200</v>
       </c>
       <c r="L32">
-        <v>9606</v>
+        <v>4173</v>
       </c>
       <c r="M32">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="N32">
-        <v>2689680</v>
+        <v>333840</v>
       </c>
       <c r="O32">
-        <v>806904</v>
+        <v>100152</v>
       </c>
       <c r="P32">
-        <v>2154433.6800000002</v>
-      </c>
-      <c r="Q32">
-        <v>178279501.7215434</v>
+        <v>267405.84000000003</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>77433385.258800402</v>
       </c>
       <c r="R32">
-        <v>8913975.0860771704</v>
-      </c>
-      <c r="S32">
-        <v>11068408.76607717</v>
-      </c>
-      <c r="T32">
-        <v>167211092.95546621</v>
+        <v>3871669.2629400198</v>
+      </c>
+      <c r="S32" s="3">
+        <v>4139075.1029400202</v>
+      </c>
+      <c r="T32" s="3">
+        <v>73294310.155860379</v>
       </c>
       <c r="U32">
-        <v>93.791541562997509</v>
+        <v>94.654663374064981</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B33">
-        <v>30</v>
-      </c>
-      <c r="C33">
-        <v>1914110.8310628589</v>
+        <v>50</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2886986.9764777748</v>
       </c>
       <c r="D33">
-        <v>1.089</v>
+        <v>1.8149999999999999</v>
       </c>
       <c r="E33">
         <v>11.942294831374801</v>
@@ -3507,63 +3547,63 @@
         <v>104.5</v>
       </c>
       <c r="G33">
-        <v>117.53129483137479</v>
+        <v>118.25729483137479</v>
       </c>
       <c r="H33">
-        <v>224967924.42557669</v>
-      </c>
-      <c r="I33">
-        <v>21304472.324335821</v>
+        <v>341407270.05167162</v>
+      </c>
+      <c r="I33" s="3">
+        <v>32132796.671411179</v>
       </c>
       <c r="J33">
-        <v>-203663452.1012409</v>
+        <v>-309274473.38026041</v>
       </c>
       <c r="K33">
         <v>200</v>
       </c>
       <c r="L33">
-        <v>9571</v>
+        <v>14435</v>
       </c>
       <c r="M33">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N33">
-        <v>574260</v>
+        <v>1443500</v>
       </c>
       <c r="O33">
-        <v>172278</v>
+        <v>433050</v>
       </c>
       <c r="P33">
-        <v>459982.26</v>
-      </c>
-      <c r="Q33">
-        <v>177629485.12263331</v>
+        <v>1156243.5</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>267912391.4171375</v>
       </c>
       <c r="R33">
-        <v>8881474.2561316639</v>
-      </c>
-      <c r="S33">
-        <v>9341456.5161316637</v>
-      </c>
-      <c r="T33">
-        <v>168288028.60650161</v>
+        <v>13395619.57085688</v>
+      </c>
+      <c r="S33" s="3">
+        <v>14551863.07085688</v>
+      </c>
+      <c r="T33" s="3">
+        <v>253360528.34628069</v>
       </c>
       <c r="U33">
-        <v>94.741043971566754</v>
+        <v>94.568424777262464</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B34">
-        <v>20</v>
-      </c>
-      <c r="C34">
-        <v>1799280.7892227459</v>
+        <v>30</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1973284.772889178</v>
       </c>
       <c r="D34">
-        <v>0.72599999999999998</v>
+        <v>1.089</v>
       </c>
       <c r="E34">
         <v>11.942294831374801</v>
@@ -3572,63 +3612,63 @@
         <v>104.5</v>
       </c>
       <c r="G34">
-        <v>117.16829483137479</v>
+        <v>117.53129483137479</v>
       </c>
       <c r="H34">
-        <v>210818661.99607939</v>
-      </c>
-      <c r="I34">
-        <v>20026388.83581255</v>
+        <v>231922714.42870039</v>
+      </c>
+      <c r="I34" s="3">
+        <v>21963091.243105881</v>
       </c>
       <c r="J34">
-        <v>-190792273.16026691</v>
+        <v>-209959623.1855945</v>
       </c>
       <c r="K34">
         <v>200</v>
       </c>
       <c r="L34">
-        <v>8997</v>
+        <v>9867</v>
       </c>
       <c r="M34">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N34">
-        <v>359880</v>
+        <v>592020</v>
       </c>
       <c r="O34">
-        <v>107964</v>
+        <v>177606</v>
       </c>
       <c r="P34">
-        <v>288263.88</v>
-      </c>
-      <c r="Q34">
-        <v>166973257.23987079</v>
+        <v>474208.02</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>183120826.92411569</v>
       </c>
       <c r="R34">
-        <v>8348662.8619935401</v>
-      </c>
-      <c r="S34">
-        <v>8636926.7419935409</v>
-      </c>
-      <c r="T34">
-        <v>158336330.4978773</v>
+        <v>9156041.346205784</v>
+      </c>
+      <c r="S34" s="3">
+        <v>9630249.3662057836</v>
+      </c>
+      <c r="T34" s="3">
+        <v>173490577.55790991</v>
       </c>
       <c r="U34">
-        <v>94.827359252155034</v>
+        <v>94.741040913824335</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B35">
-        <v>80</v>
-      </c>
-      <c r="C35">
-        <v>1674515.3341640159</v>
+        <v>10</v>
+      </c>
+      <c r="C35" s="2">
+        <v>438270.56791048631</v>
       </c>
       <c r="D35">
-        <v>2.9039999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E35">
         <v>11.942294831374801</v>
@@ -3637,63 +3677,63 @@
         <v>104.5</v>
       </c>
       <c r="G35">
-        <v>119.34629483137481</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H35">
-        <v>199847200.77079669</v>
-      </c>
-      <c r="I35">
-        <v>18637722.02446812</v>
+        <v>51192322.900698423</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4878047.3069238234</v>
       </c>
       <c r="J35">
-        <v>-181209478.74632859</v>
+        <v>-46314275.593774602</v>
       </c>
       <c r="K35">
         <v>200</v>
       </c>
       <c r="L35">
-        <v>8373</v>
+        <v>2192</v>
       </c>
       <c r="M35">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="N35">
-        <v>1339680</v>
+        <v>43840</v>
       </c>
       <c r="O35">
-        <v>401904</v>
+        <v>13152</v>
       </c>
       <c r="P35">
-        <v>1073083.68</v>
-      </c>
-      <c r="Q35">
-        <v>155395023.01042071</v>
+        <v>35115.839999999997</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>40671508.702093132</v>
       </c>
       <c r="R35">
-        <v>7769751.1505210334</v>
-      </c>
-      <c r="S35">
-        <v>8842834.8305210341</v>
-      </c>
-      <c r="T35">
-        <v>146552188.1798996</v>
+        <v>2033575.435104656</v>
+      </c>
+      <c r="S35" s="3">
+        <v>2068691.2751046559</v>
+      </c>
+      <c r="T35" s="3">
+        <v>38602817.426988482</v>
       </c>
       <c r="U35">
-        <v>94.309447845103733</v>
+        <v>94.913659853984726</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B36">
-        <v>30</v>
-      </c>
-      <c r="C36">
-        <v>1534972.3896503481</v>
+        <v>80</v>
+      </c>
+      <c r="C36" s="2">
+        <v>552667.70606108301</v>
       </c>
       <c r="D36">
-        <v>1.089</v>
+        <v>2.9039999999999999</v>
       </c>
       <c r="E36">
         <v>11.942294831374801</v>
@@ -3702,63 +3742,63 @@
         <v>104.5</v>
       </c>
       <c r="G36">
-        <v>117.53129483137479</v>
+        <v>119.34629483137481</v>
       </c>
       <c r="H36">
-        <v>180407292.4860149</v>
-      </c>
-      <c r="I36">
-        <v>17084578.522429109</v>
+        <v>65958842.991345592</v>
+      </c>
+      <c r="I36" s="3">
+        <v>6151312.4826708864</v>
       </c>
       <c r="J36">
-        <v>-163322713.96358579</v>
+        <v>-59807530.508674704</v>
       </c>
       <c r="K36">
         <v>200</v>
       </c>
       <c r="L36">
-        <v>7675</v>
+        <v>2764</v>
       </c>
       <c r="M36">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="N36">
-        <v>460500</v>
+        <v>442240</v>
       </c>
       <c r="O36">
-        <v>138150</v>
+        <v>132672</v>
       </c>
       <c r="P36">
-        <v>368860.5</v>
-      </c>
-      <c r="Q36">
-        <v>142445437.7595523</v>
+        <v>354234.24</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>51287563.122468501</v>
       </c>
       <c r="R36">
-        <v>7122271.8879776122</v>
-      </c>
-      <c r="S36">
-        <v>7491132.3879776122</v>
-      </c>
-      <c r="T36">
-        <v>134954305.3715747</v>
+        <v>2564378.1561234249</v>
+      </c>
+      <c r="S36" s="3">
+        <v>2918612.3961234251</v>
+      </c>
+      <c r="T36" s="3">
+        <v>48368950.726345077</v>
       </c>
       <c r="U36">
-        <v>94.741051376722481</v>
+        <v>94.309317467172065</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B37">
-        <v>100</v>
-      </c>
-      <c r="C37">
-        <v>1534972.3896503481</v>
+        <v>40</v>
+      </c>
+      <c r="C37" s="2">
+        <v>347648.47067168099</v>
       </c>
       <c r="D37">
-        <v>3.63</v>
+        <v>1.452</v>
       </c>
       <c r="E37">
         <v>11.942294831374801</v>
@@ -3767,63 +3807,63 @@
         <v>104.5</v>
       </c>
       <c r="G37">
-        <v>120.0722948313748</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H37">
-        <v>184307657.32811639</v>
-      </c>
-      <c r="I37">
-        <v>17084578.522429109</v>
+        <v>40985771.299043722</v>
+      </c>
+      <c r="I37" s="3">
+        <v>3869403.538096</v>
       </c>
       <c r="J37">
-        <v>-167223078.80568731</v>
+        <v>-37116367.760947712</v>
       </c>
       <c r="K37">
         <v>200</v>
       </c>
       <c r="L37">
-        <v>7675</v>
+        <v>1739</v>
       </c>
       <c r="M37">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="N37">
-        <v>1535000</v>
+        <v>139120</v>
       </c>
       <c r="O37">
-        <v>460500</v>
+        <v>41736</v>
       </c>
       <c r="P37">
-        <v>1229535</v>
-      </c>
-      <c r="Q37">
-        <v>142445437.7595523</v>
+        <v>111435.12</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>32261778.078331999</v>
       </c>
       <c r="R37">
-        <v>7122271.8879776122</v>
-      </c>
-      <c r="S37">
-        <v>8351806.8879776122</v>
-      </c>
-      <c r="T37">
-        <v>134093630.8715747</v>
+        <v>1613088.9039165999</v>
+      </c>
+      <c r="S37" s="3">
+        <v>1724524.0239166</v>
+      </c>
+      <c r="T37" s="3">
+        <v>30537254.054415401</v>
       </c>
       <c r="U37">
-        <v>94.136837922408262</v>
+        <v>94.654590891644489</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>20</v>
-      </c>
-      <c r="C38">
-        <v>1534972.3896503481</v>
+        <v>40</v>
+      </c>
+      <c r="C38" s="2">
+        <v>704408.95076759241</v>
       </c>
       <c r="D38">
-        <v>0.72599999999999998</v>
+        <v>1.452</v>
       </c>
       <c r="E38">
         <v>11.942294831374801</v>
@@ -3832,63 +3872,63 @@
         <v>104.5</v>
       </c>
       <c r="G38">
-        <v>117.16829483137479</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H38">
-        <v>179850097.5085718</v>
-      </c>
-      <c r="I38">
-        <v>17084578.522429109</v>
+        <v>83045796.52365391</v>
+      </c>
+      <c r="I38" s="3">
+        <v>7840225.7346349973</v>
       </c>
       <c r="J38">
-        <v>-162765518.98614269</v>
+        <v>-75205570.789018914</v>
       </c>
       <c r="K38">
         <v>200</v>
       </c>
       <c r="L38">
-        <v>7675</v>
+        <v>3523</v>
       </c>
       <c r="M38">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N38">
-        <v>307000</v>
+        <v>281840</v>
       </c>
       <c r="O38">
-        <v>92100</v>
+        <v>84552</v>
       </c>
       <c r="P38">
-        <v>245907</v>
-      </c>
-      <c r="Q38">
-        <v>142445437.7595523</v>
+        <v>225753.84</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>65369150.631232567</v>
       </c>
       <c r="R38">
-        <v>7122271.8879776122</v>
-      </c>
-      <c r="S38">
-        <v>7368178.8879776122</v>
-      </c>
-      <c r="T38">
-        <v>135077258.8715747</v>
+        <v>3268457.531561628</v>
+      </c>
+      <c r="S38" s="3">
+        <v>3494211.3715616278</v>
+      </c>
+      <c r="T38" s="3">
+        <v>61874939.259670943</v>
       </c>
       <c r="U38">
-        <v>94.827367584481664</v>
+        <v>94.654647738543289</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B39">
-        <v>40</v>
-      </c>
-      <c r="C39">
-        <v>1530064.6578074801</v>
+        <v>20</v>
+      </c>
+      <c r="C39" s="2">
+        <v>131481.1703731459</v>
       </c>
       <c r="D39">
-        <v>1.452</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E39">
         <v>11.942294831374801</v>
@@ -3897,63 +3937,63 @@
         <v>104.5</v>
       </c>
       <c r="G39">
-        <v>117.89429483137479</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H39">
-        <v>180385893.87862161</v>
-      </c>
-      <c r="I39">
-        <v>17029954.393290471</v>
+        <v>15405424.53505498</v>
+      </c>
+      <c r="I39" s="3">
+        <v>1463414.1920771471</v>
       </c>
       <c r="J39">
-        <v>-163355939.48533109</v>
+        <v>-13942010.342977829</v>
       </c>
       <c r="K39">
         <v>200</v>
       </c>
       <c r="L39">
-        <v>7651</v>
+        <v>658</v>
       </c>
       <c r="M39">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N39">
-        <v>612080</v>
+        <v>26320</v>
       </c>
       <c r="O39">
-        <v>183624</v>
+        <v>7896</v>
       </c>
       <c r="P39">
-        <v>490276.08</v>
-      </c>
-      <c r="Q39">
-        <v>141990000.24453411</v>
+        <v>21082.32</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>12201452.61062794</v>
       </c>
       <c r="R39">
-        <v>7099500.0122267054</v>
-      </c>
-      <c r="S39">
-        <v>7589776.0922267046</v>
-      </c>
-      <c r="T39">
-        <v>134400224.15230739</v>
+        <v>610072.63053139683</v>
+      </c>
+      <c r="S39" s="3">
+        <v>631154.95053139678</v>
+      </c>
+      <c r="T39" s="3">
+        <v>11570297.660096539</v>
       </c>
       <c r="U39">
-        <v>94.654710839386112</v>
+        <v>94.827214671295465</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="B40">
-        <v>50</v>
-      </c>
-      <c r="C40">
-        <v>1530064.6578074801</v>
+        <v>10</v>
+      </c>
+      <c r="C40" s="2">
+        <v>158253.01837637831</v>
       </c>
       <c r="D40">
-        <v>1.8149999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E40">
         <v>11.942294831374801</v>
@@ -3962,63 +4002,63 @@
         <v>104.5</v>
       </c>
       <c r="G40">
-        <v>118.25729483137479</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H40">
-        <v>180941307.34940571</v>
-      </c>
-      <c r="I40">
-        <v>17029954.393290471</v>
+        <v>18484790.469407842</v>
+      </c>
+      <c r="I40" s="3">
+        <v>1761390.717574097</v>
       </c>
       <c r="J40">
-        <v>-163911352.95611519</v>
+        <v>-16723399.751833741</v>
       </c>
       <c r="K40">
         <v>200</v>
       </c>
       <c r="L40">
-        <v>7651</v>
+        <v>792</v>
       </c>
       <c r="M40">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="N40">
-        <v>765100</v>
+        <v>15840</v>
       </c>
       <c r="O40">
-        <v>229530</v>
+        <v>4752</v>
       </c>
       <c r="P40">
-        <v>612845.1</v>
-      </c>
-      <c r="Q40">
-        <v>141990000.24453411</v>
+        <v>12687.84</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>14685880.1053279</v>
       </c>
       <c r="R40">
-        <v>7099500.0122267054</v>
-      </c>
-      <c r="S40">
-        <v>7712345.1122267041</v>
-      </c>
-      <c r="T40">
-        <v>134277655.13230741</v>
+        <v>734294.00526639516</v>
+      </c>
+      <c r="S40" s="3">
+        <v>746981.84526639513</v>
+      </c>
+      <c r="T40" s="3">
+        <v>13938898.26006151</v>
       </c>
       <c r="U40">
-        <v>94.568388549232665</v>
+        <v>94.913605177837482</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B41">
-        <v>10</v>
-      </c>
-      <c r="C41">
-        <v>1528495.805373763</v>
+        <v>20</v>
+      </c>
+      <c r="C41" s="2">
+        <v>494540.6824261822</v>
       </c>
       <c r="D41">
-        <v>0.36299999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E41">
         <v>11.942294831374801</v>
@@ -4027,63 +4067,63 @@
         <v>104.5</v>
       </c>
       <c r="G41">
-        <v>116.80529483137479</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H41">
-        <v>178536403.19520199</v>
-      </c>
-      <c r="I41">
-        <v>17012492.72246521</v>
+        <v>57944488.484620214</v>
+      </c>
+      <c r="I41" s="3">
+        <v>5504345.9924190529</v>
       </c>
       <c r="J41">
-        <v>-161523910.47273681</v>
+        <v>-52440142.492201149</v>
       </c>
       <c r="K41">
         <v>200</v>
       </c>
       <c r="L41">
-        <v>7643</v>
+        <v>2473</v>
       </c>
       <c r="M41">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N41">
-        <v>152860</v>
+        <v>98920</v>
       </c>
       <c r="O41">
-        <v>45858</v>
+        <v>29676</v>
       </c>
       <c r="P41">
-        <v>122440.86</v>
-      </c>
-      <c r="Q41">
-        <v>141844410.73868519</v>
+        <v>79234.92</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>45893375.329149708</v>
       </c>
       <c r="R41">
-        <v>7092220.5369342566</v>
-      </c>
-      <c r="S41">
-        <v>7214661.3969342578</v>
-      </c>
-      <c r="T41">
-        <v>134629749.34175089</v>
+        <v>2294668.766457486</v>
+      </c>
+      <c r="S41" s="3">
+        <v>2373903.686457485</v>
+      </c>
+      <c r="T41" s="3">
+        <v>43519471.642692223</v>
       </c>
       <c r="U41">
-        <v>94.913679460923149</v>
+        <v>94.827349983670359</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="B42">
-        <v>10</v>
-      </c>
-      <c r="C42">
-        <v>1421069.1547954229</v>
+        <v>70</v>
+      </c>
+      <c r="C42" s="2">
+        <v>6113983.22149505</v>
       </c>
       <c r="D42">
-        <v>0.36299999999999999</v>
+        <v>2.5409999999999999</v>
       </c>
       <c r="E42">
         <v>11.942294831374801</v>
@@ -4092,63 +4132,63 @@
         <v>104.5</v>
       </c>
       <c r="G42">
-        <v>116.80529483137479</v>
+        <v>118.98329483137481</v>
       </c>
       <c r="H42">
-        <v>165988401.60165191</v>
-      </c>
-      <c r="I42">
-        <v>15816810.598420439</v>
+        <v>727461868.23722422</v>
+      </c>
+      <c r="I42" s="3">
+        <v>68049970.889860839</v>
       </c>
       <c r="J42">
-        <v>-150171591.0032315</v>
+        <v>-659411897.34736335</v>
       </c>
       <c r="K42">
         <v>200</v>
       </c>
       <c r="L42">
-        <v>7106</v>
+        <v>30570</v>
       </c>
       <c r="M42">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="N42">
-        <v>142120</v>
+        <v>4279800</v>
       </c>
       <c r="O42">
-        <v>42636</v>
+        <v>1283940</v>
       </c>
       <c r="P42">
-        <v>113838.12</v>
-      </c>
-      <c r="Q42">
-        <v>131875217.5650152</v>
+        <v>3428119.8</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>567377642.95474064</v>
       </c>
       <c r="R42">
-        <v>6593760.878250761</v>
-      </c>
-      <c r="S42">
-        <v>6707598.9982507611</v>
-      </c>
-      <c r="T42">
-        <v>125167618.5667645</v>
+        <v>28368882.14773703</v>
+      </c>
+      <c r="S42" s="3">
+        <v>31797001.947737031</v>
+      </c>
+      <c r="T42" s="3">
+        <v>535580641.00700361</v>
       </c>
       <c r="U42">
-        <v>94.913677397389776</v>
+        <v>94.395795755689747</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B43">
-        <v>100</v>
-      </c>
-      <c r="C43">
-        <v>1222796.64429901</v>
+        <v>80</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1674515.3341640159</v>
       </c>
       <c r="D43">
-        <v>3.63</v>
+        <v>2.9039999999999999</v>
       </c>
       <c r="E43">
         <v>11.942294831374801</v>
@@ -4157,63 +4197,63 @@
         <v>104.5</v>
       </c>
       <c r="G43">
-        <v>120.0722948313748</v>
+        <v>119.34629483137481</v>
       </c>
       <c r="H43">
-        <v>146823999.19308639</v>
-      </c>
-      <c r="I43">
-        <v>13609994.17797216</v>
+        <v>199847200.77079669</v>
+      </c>
+      <c r="I43" s="3">
+        <v>18637722.02446812</v>
       </c>
       <c r="J43">
-        <v>-133214005.01511431</v>
+        <v>-181209478.74632859</v>
       </c>
       <c r="K43">
         <v>200</v>
       </c>
       <c r="L43">
-        <v>6114</v>
+        <v>8373</v>
       </c>
       <c r="M43">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="N43">
-        <v>1222800</v>
+        <v>1339680</v>
       </c>
       <c r="O43">
-        <v>366840</v>
+        <v>401904</v>
       </c>
       <c r="P43">
-        <v>979462.79999999993</v>
-      </c>
-      <c r="Q43">
-        <v>113475528.5909481</v>
+        <v>1073083.68</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>155395023.01042071</v>
       </c>
       <c r="R43">
-        <v>5673776.4295474049</v>
-      </c>
-      <c r="S43">
-        <v>6653239.2295474047</v>
-      </c>
-      <c r="T43">
-        <v>106822289.36140069</v>
+        <v>7769751.1505210334</v>
+      </c>
+      <c r="S43" s="3">
+        <v>8842834.8305210341</v>
+      </c>
+      <c r="T43" s="3">
+        <v>146552188.1798996</v>
       </c>
       <c r="U43">
-        <v>94.136851079556791</v>
+        <v>94.309447845103733</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B44">
-        <v>10</v>
-      </c>
-      <c r="C44">
-        <v>1222796.64429901</v>
+        <v>90</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1020043.1052049859</v>
       </c>
       <c r="D44">
-        <v>0.36299999999999999</v>
+        <v>3.2669999999999999</v>
       </c>
       <c r="E44">
         <v>11.942294831374801</v>
@@ -4222,63 +4262,63 @@
         <v>104.5</v>
       </c>
       <c r="G44">
-        <v>116.80529483137479</v>
+        <v>119.70929483137481</v>
       </c>
       <c r="H44">
-        <v>142829122.55616161</v>
-      </c>
-      <c r="I44">
-        <v>13609994.17797216</v>
+        <v>122108640.8216947</v>
+      </c>
+      <c r="I44" s="3">
+        <v>11353302.92886031</v>
       </c>
       <c r="J44">
-        <v>-129219128.3781894</v>
+        <v>-110755337.8928344</v>
       </c>
       <c r="K44">
         <v>200</v>
       </c>
       <c r="L44">
-        <v>6114</v>
+        <v>5101</v>
       </c>
       <c r="M44">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="N44">
-        <v>122280</v>
+        <v>918180</v>
       </c>
       <c r="O44">
-        <v>36684</v>
+        <v>275454</v>
       </c>
       <c r="P44">
-        <v>97946.28</v>
-      </c>
-      <c r="Q44">
-        <v>113475528.5909481</v>
+        <v>735462.17999999993</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>94660000.163022712</v>
       </c>
       <c r="R44">
-        <v>5673776.4295474049</v>
-      </c>
-      <c r="S44">
-        <v>5771722.7095474051</v>
-      </c>
-      <c r="T44">
-        <v>107703805.8814007</v>
+        <v>4733000.0081511354</v>
+      </c>
+      <c r="S44" s="3">
+        <v>5468462.1881511351</v>
+      </c>
+      <c r="T44" s="3">
+        <v>89191537.974871576</v>
       </c>
       <c r="U44">
-        <v>94.913685107955672</v>
+        <v>94.223048617437783</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B45">
-        <v>10</v>
-      </c>
-      <c r="C45">
-        <v>1057686.228970353</v>
+        <v>40</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1530064.6578074801</v>
       </c>
       <c r="D45">
-        <v>0.36299999999999999</v>
+        <v>1.452</v>
       </c>
       <c r="E45">
         <v>11.942294831374801</v>
@@ -4287,63 +4327,63 @@
         <v>104.5</v>
       </c>
       <c r="G45">
-        <v>116.80529483137479</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H45">
-        <v>123543351.813967</v>
-      </c>
-      <c r="I45">
-        <v>11772279.132038411</v>
+        <v>180385893.87862161</v>
+      </c>
+      <c r="I45" s="3">
+        <v>17029954.393290471</v>
       </c>
       <c r="J45">
-        <v>-111771072.6819286</v>
+        <v>-163355939.48533109</v>
       </c>
       <c r="K45">
         <v>200</v>
       </c>
       <c r="L45">
-        <v>5289</v>
+        <v>7651</v>
       </c>
       <c r="M45">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N45">
-        <v>105780</v>
+        <v>612080</v>
       </c>
       <c r="O45">
-        <v>31734</v>
+        <v>183624</v>
       </c>
       <c r="P45">
-        <v>84729.78</v>
-      </c>
-      <c r="Q45">
-        <v>98153282.048448712</v>
+        <v>490276.08</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>141990000.24453411</v>
       </c>
       <c r="R45">
-        <v>4907664.1024224358</v>
-      </c>
-      <c r="S45">
-        <v>4992393.882422436</v>
-      </c>
-      <c r="T45">
-        <v>93160888.166026279</v>
+        <v>7099500.0122267054</v>
+      </c>
+      <c r="S45" s="3">
+        <v>7589776.0922267046</v>
+      </c>
+      <c r="T45" s="3">
+        <v>134400224.15230739</v>
       </c>
       <c r="U45">
-        <v>94.913676060309257</v>
+        <v>94.654710839386112</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B46">
-        <v>20</v>
-      </c>
-      <c r="C46">
-        <v>1052418.5455408951</v>
+        <v>100</v>
+      </c>
+      <c r="C46" s="2">
+        <v>509315.28864071658</v>
       </c>
       <c r="D46">
-        <v>0.72599999999999998</v>
+        <v>3.63</v>
       </c>
       <c r="E46">
         <v>11.942294831374801</v>
@@ -4352,63 +4392,63 @@
         <v>104.5</v>
       </c>
       <c r="G46">
-        <v>117.16829483137479</v>
+        <v>120.0722948313748</v>
       </c>
       <c r="H46">
-        <v>123310086.42994221</v>
-      </c>
-      <c r="I46">
-        <v>11713648.662989801</v>
+        <v>61154655.499794878</v>
+      </c>
+      <c r="I46" s="3">
+        <v>5668790.5920171477</v>
       </c>
       <c r="J46">
-        <v>-111596437.7669524</v>
+        <v>-55485864.907777727</v>
       </c>
       <c r="K46">
         <v>200</v>
       </c>
       <c r="L46">
-        <v>5263</v>
+        <v>2547</v>
       </c>
       <c r="M46">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="N46">
-        <v>210520</v>
+        <v>509400</v>
       </c>
       <c r="O46">
-        <v>63156</v>
+        <v>152820</v>
       </c>
       <c r="P46">
-        <v>168626.52</v>
-      </c>
-      <c r="Q46">
-        <v>97664441.026195064</v>
+        <v>408029.4</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>47264458.785858497</v>
       </c>
       <c r="R46">
-        <v>4883222.0513097532</v>
-      </c>
-      <c r="S46">
-        <v>5051848.5713097528</v>
-      </c>
-      <c r="T46">
-        <v>92612592.454885304</v>
+        <v>2363222.9392929249</v>
+      </c>
+      <c r="S46" s="3">
+        <v>2771252.3392929249</v>
+      </c>
+      <c r="T46" s="3">
+        <v>44493206.446565583</v>
       </c>
       <c r="U46">
-        <v>94.827340925491228</v>
+        <v>94.136709886283342</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B47">
-        <v>90</v>
-      </c>
-      <c r="C47">
-        <v>1020043.1052049859</v>
+        <v>10</v>
+      </c>
+      <c r="C47" s="2">
+        <v>4263207.4643862695</v>
       </c>
       <c r="D47">
-        <v>3.2669999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E47">
         <v>11.942294831374801</v>
@@ -4417,60 +4457,60 @@
         <v>104.5</v>
       </c>
       <c r="G47">
-        <v>119.70929483137481</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H47">
-        <v>122108640.8216947</v>
-      </c>
-      <c r="I47">
-        <v>11353302.92886031</v>
+        <v>497965204.80495578</v>
+      </c>
+      <c r="I47" s="3">
+        <v>47450431.795261323</v>
       </c>
       <c r="J47">
-        <v>-110755337.8928344</v>
+        <v>-450514773.00969452</v>
       </c>
       <c r="K47">
         <v>200</v>
       </c>
       <c r="L47">
-        <v>5101</v>
+        <v>21317</v>
       </c>
       <c r="M47">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="N47">
-        <v>918180</v>
+        <v>426340</v>
       </c>
       <c r="O47">
-        <v>275454</v>
+        <v>127902</v>
       </c>
       <c r="P47">
-        <v>735462.17999999993</v>
-      </c>
-      <c r="Q47">
-        <v>94660000.163022712</v>
+        <v>341498.34</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>395625652.69504571</v>
       </c>
       <c r="R47">
-        <v>4733000.0081511354</v>
-      </c>
-      <c r="S47">
-        <v>5468462.1881511351</v>
-      </c>
-      <c r="T47">
-        <v>89191537.974871576</v>
+        <v>19781282.634752281</v>
+      </c>
+      <c r="S47" s="3">
+        <v>20122780.974752281</v>
+      </c>
+      <c r="T47" s="3">
+        <v>375502871.7202934</v>
       </c>
       <c r="U47">
-        <v>94.223048617437783</v>
+        <v>94.913681446672214</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>20</v>
       </c>
-      <c r="C48">
-        <v>981660.56362576562</v>
+      <c r="C48" s="2">
+        <v>791265.09188189148</v>
       </c>
       <c r="D48">
         <v>0.72599999999999998</v>
@@ -4485,60 +4525,60 @@
         <v>117.16829483137479</v>
       </c>
       <c r="H48">
-        <v>115019494.3432373</v>
-      </c>
-      <c r="I48">
-        <v>10926096.84364208</v>
+        <v>92711181.575392321</v>
+      </c>
+      <c r="I48" s="3">
+        <v>8806953.5878704842</v>
       </c>
       <c r="J48">
-        <v>-104093397.4995952</v>
+        <v>-83904227.987521842</v>
       </c>
       <c r="K48">
         <v>200</v>
       </c>
       <c r="L48">
-        <v>4909</v>
+        <v>3957</v>
       </c>
       <c r="M48">
         <v>40</v>
       </c>
       <c r="N48">
-        <v>196360</v>
+        <v>158280</v>
       </c>
       <c r="O48">
-        <v>58908</v>
+        <v>47484</v>
       </c>
       <c r="P48">
-        <v>157284.35999999999</v>
-      </c>
-      <c r="Q48">
-        <v>91098100.304471046</v>
+        <v>126782.28</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>73429400.526639521</v>
       </c>
       <c r="R48">
-        <v>4554905.0152235515</v>
-      </c>
-      <c r="S48">
-        <v>4712189.3752235528</v>
-      </c>
-      <c r="T48">
-        <v>86385910.929247499</v>
+        <v>3671470.0263319761</v>
+      </c>
+      <c r="S48" s="3">
+        <v>3798252.3063319759</v>
+      </c>
+      <c r="T48" s="3">
+        <v>69631148.220307544</v>
       </c>
       <c r="U48">
-        <v>94.827346169157948</v>
+        <v>94.827341256920647</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B49">
-        <v>20</v>
-      </c>
-      <c r="C49">
-        <v>917034.97615424264</v>
+        <v>40</v>
+      </c>
+      <c r="C49" s="2">
+        <v>6878231.1241819309</v>
       </c>
       <c r="D49">
-        <v>0.72599999999999998</v>
+        <v>1.452</v>
       </c>
       <c r="E49">
         <v>11.942294831374801</v>
@@ -4547,63 +4587,63 @@
         <v>104.5</v>
       </c>
       <c r="G49">
-        <v>117.16829483137479</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H49">
-        <v>107447424.456723</v>
-      </c>
-      <c r="I49">
-        <v>10206799.91611439</v>
+        <v>810904208.07264304</v>
+      </c>
+      <c r="I49" s="3">
+        <v>76556217.251093432</v>
       </c>
       <c r="J49">
-        <v>-97240624.540608659</v>
+        <v>-734347990.82154965</v>
       </c>
       <c r="K49">
         <v>200</v>
       </c>
       <c r="L49">
-        <v>4586</v>
+        <v>34392</v>
       </c>
       <c r="M49">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N49">
-        <v>183440</v>
+        <v>2751360</v>
       </c>
       <c r="O49">
-        <v>55032</v>
+        <v>825408</v>
       </c>
       <c r="P49">
-        <v>146935.44</v>
-      </c>
-      <c r="Q49">
-        <v>85100845.787113711</v>
+        <v>2203839.36</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>638299848.32408321</v>
       </c>
       <c r="R49">
-        <v>4255042.2893556859</v>
-      </c>
-      <c r="S49">
-        <v>4401977.7293556863</v>
-      </c>
-      <c r="T49">
-        <v>80698868.057758018</v>
+        <v>31914992.416204158</v>
+      </c>
+      <c r="S49" s="3">
+        <v>34118831.776204161</v>
+      </c>
+      <c r="T49" s="3">
+        <v>604181016.5478791</v>
       </c>
       <c r="U49">
-        <v>94.827339624370381</v>
+        <v>94.654732902446028</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50">
         <v>50</v>
       </c>
-      <c r="B50">
-        <v>60</v>
-      </c>
-      <c r="C50">
-        <v>837257.66708200797</v>
+      <c r="C50" s="2">
+        <v>4341226.5003561927</v>
       </c>
       <c r="D50">
-        <v>2.1779999999999999</v>
+        <v>1.8149999999999999</v>
       </c>
       <c r="E50">
         <v>11.942294831374801</v>
@@ -4612,63 +4652,63 @@
         <v>104.5</v>
       </c>
       <c r="G50">
-        <v>118.62029483137481</v>
+        <v>118.25729483137479</v>
       </c>
       <c r="H50">
-        <v>99315751.319096833</v>
-      </c>
-      <c r="I50">
-        <v>9318861.012234062</v>
+        <v>513381702.18239969</v>
+      </c>
+      <c r="I50" s="3">
+        <v>48318800.73483295</v>
       </c>
       <c r="J50">
-        <v>-89996890.306862772</v>
+        <v>-465062901.44756669</v>
       </c>
       <c r="K50">
         <v>200</v>
       </c>
       <c r="L50">
-        <v>4187</v>
+        <v>21707</v>
       </c>
       <c r="M50">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N50">
-        <v>502440</v>
+        <v>2170700</v>
       </c>
       <c r="O50">
-        <v>150732</v>
+        <v>651210</v>
       </c>
       <c r="P50">
-        <v>402454.44</v>
-      </c>
-      <c r="Q50">
-        <v>77697511.50521034</v>
+        <v>1738730.7</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>402865819.2330547</v>
       </c>
       <c r="R50">
-        <v>3884875.5752605172</v>
-      </c>
-      <c r="S50">
-        <v>4287330.0152605167</v>
-      </c>
-      <c r="T50">
-        <v>73410181.489949822</v>
+        <v>20143290.96165273</v>
+      </c>
+      <c r="S50" s="3">
+        <v>21882021.661652729</v>
+      </c>
+      <c r="T50" s="3">
+        <v>380983797.57140201</v>
       </c>
       <c r="U50">
-        <v>94.482024028564908</v>
+        <v>94.568409476060779</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B51">
-        <v>40</v>
-      </c>
-      <c r="C51">
-        <v>834411.47908190091</v>
+        <v>10</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2009816.3726160021</v>
       </c>
       <c r="D51">
-        <v>1.452</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E51">
         <v>11.942294831374801</v>
@@ -4677,63 +4717,63 @@
         <v>104.5</v>
       </c>
       <c r="G51">
-        <v>117.89429483137479</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H51">
-        <v>98372352.925565153</v>
-      </c>
-      <c r="I51">
-        <v>9287182.3170957733</v>
+        <v>234757193.9603363</v>
+      </c>
+      <c r="I51" s="3">
+        <v>22369695.940552611</v>
       </c>
       <c r="J51">
-        <v>-89085170.608469382</v>
+        <v>-212387498.01978371</v>
       </c>
       <c r="K51">
         <v>200</v>
       </c>
       <c r="L51">
-        <v>4173</v>
+        <v>10050</v>
       </c>
       <c r="M51">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N51">
-        <v>333840</v>
+        <v>201000</v>
       </c>
       <c r="O51">
-        <v>100152</v>
+        <v>60300</v>
       </c>
       <c r="P51">
-        <v>267405.84000000003</v>
-      </c>
-      <c r="Q51">
-        <v>77433385.258800402</v>
+        <v>161001</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>186510959.37876499</v>
       </c>
       <c r="R51">
-        <v>3871669.2629400198</v>
-      </c>
-      <c r="S51">
-        <v>4139075.1029400202</v>
-      </c>
-      <c r="T51">
-        <v>73294310.155860379</v>
+        <v>9325547.9689382482</v>
+      </c>
+      <c r="S51" s="3">
+        <v>9486548.9689382482</v>
+      </c>
+      <c r="T51" s="3">
+        <v>177024410.4098267</v>
       </c>
       <c r="U51">
-        <v>94.654663374064981</v>
+        <v>94.913677458667166</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B52">
-        <v>20</v>
-      </c>
-      <c r="C52">
-        <v>791265.09188189148</v>
+        <v>10</v>
+      </c>
+      <c r="C52" s="2">
+        <v>547838.20988810796</v>
       </c>
       <c r="D52">
-        <v>0.72599999999999998</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E52">
         <v>11.942294831374801</v>
@@ -4742,63 +4782,63 @@
         <v>104.5</v>
       </c>
       <c r="G52">
-        <v>117.16829483137479</v>
+        <v>116.80529483137479</v>
       </c>
       <c r="H52">
-        <v>92711181.575392321</v>
-      </c>
-      <c r="I52">
-        <v>8806953.5878704842</v>
+        <v>63990403.625873037</v>
+      </c>
+      <c r="I52" s="3">
+        <v>6097559.1336547798</v>
       </c>
       <c r="J52">
-        <v>-83904227.987521842</v>
+        <v>-57892844.492218263</v>
       </c>
       <c r="K52">
         <v>200</v>
       </c>
       <c r="L52">
-        <v>3957</v>
+        <v>2740</v>
       </c>
       <c r="M52">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N52">
-        <v>158280</v>
+        <v>54800</v>
       </c>
       <c r="O52">
-        <v>47484</v>
+        <v>16440</v>
       </c>
       <c r="P52">
-        <v>126782.28</v>
-      </c>
-      <c r="Q52">
-        <v>73429400.526639521</v>
+        <v>43894.8</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>50839385.87761642</v>
       </c>
       <c r="R52">
-        <v>3671470.0263319761</v>
-      </c>
-      <c r="S52">
-        <v>3798252.3063319759</v>
-      </c>
-      <c r="T52">
-        <v>69631148.220307544</v>
+        <v>2541969.2938808212</v>
+      </c>
+      <c r="S52" s="3">
+        <v>2585864.093880821</v>
+      </c>
+      <c r="T52" s="3">
+        <v>48253521.783735603</v>
       </c>
       <c r="U52">
-        <v>94.827341256920647</v>
+        <v>94.913659853984726</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B53">
-        <v>40</v>
-      </c>
-      <c r="C53">
-        <v>704408.95076759241</v>
+        <v>20</v>
+      </c>
+      <c r="C53" s="2">
+        <v>917034.97615424264</v>
       </c>
       <c r="D53">
-        <v>1.452</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E53">
         <v>11.942294831374801</v>
@@ -4807,63 +4847,63 @@
         <v>104.5</v>
       </c>
       <c r="G53">
-        <v>117.89429483137479</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H53">
-        <v>83045796.52365391</v>
-      </c>
-      <c r="I53">
-        <v>7840225.7346349973</v>
+        <v>107447424.456723</v>
+      </c>
+      <c r="I53" s="3">
+        <v>10206799.91611439</v>
       </c>
       <c r="J53">
-        <v>-75205570.789018914</v>
+        <v>-97240624.540608659</v>
       </c>
       <c r="K53">
         <v>200</v>
       </c>
       <c r="L53">
-        <v>3523</v>
+        <v>4586</v>
       </c>
       <c r="M53">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N53">
-        <v>281840</v>
+        <v>183440</v>
       </c>
       <c r="O53">
-        <v>84552</v>
+        <v>55032</v>
       </c>
       <c r="P53">
-        <v>225753.84</v>
-      </c>
-      <c r="Q53">
-        <v>65369150.631232567</v>
+        <v>146935.44</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>85100845.787113711</v>
       </c>
       <c r="R53">
-        <v>3268457.531561628</v>
-      </c>
-      <c r="S53">
-        <v>3494211.3715616278</v>
-      </c>
-      <c r="T53">
-        <v>61874939.259670943</v>
+        <v>4255042.2893556859</v>
+      </c>
+      <c r="S53" s="3">
+        <v>4401977.7293556863</v>
+      </c>
+      <c r="T53" s="3">
+        <v>80698868.057758018</v>
       </c>
       <c r="U53">
-        <v>94.654647738543289</v>
+        <v>94.827339624370381</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B54">
-        <v>70</v>
-      </c>
-      <c r="C54">
-        <v>637526.94075311639</v>
+        <v>20</v>
+      </c>
+      <c r="C54" s="2">
+        <v>981660.56362576562</v>
       </c>
       <c r="D54">
-        <v>2.5409999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E54">
         <v>11.942294831374801</v>
@@ -4872,63 +4912,63 @@
         <v>104.5</v>
       </c>
       <c r="G54">
-        <v>118.98329483137481</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H54">
-        <v>75855055.954572454</v>
-      </c>
-      <c r="I54">
-        <v>7095814.3305376954</v>
+        <v>115019494.3432373</v>
+      </c>
+      <c r="I54" s="3">
+        <v>10926096.84364208</v>
       </c>
       <c r="J54">
-        <v>-68759241.624034762</v>
+        <v>-104093397.4995952</v>
       </c>
       <c r="K54">
         <v>200</v>
       </c>
       <c r="L54">
-        <v>3188</v>
+        <v>4909</v>
       </c>
       <c r="M54">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="N54">
-        <v>446320</v>
+        <v>196360</v>
       </c>
       <c r="O54">
-        <v>133896</v>
+        <v>58908</v>
       </c>
       <c r="P54">
-        <v>357502.32</v>
-      </c>
-      <c r="Q54">
-        <v>59162500.101889201</v>
+        <v>157284.35999999999</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>91098100.304471046</v>
       </c>
       <c r="R54">
-        <v>2958125.0050944602</v>
-      </c>
-      <c r="S54">
-        <v>3315627.32509446</v>
-      </c>
-      <c r="T54">
-        <v>55846872.776794739</v>
+        <v>4554905.0152235515</v>
+      </c>
+      <c r="S54" s="3">
+        <v>4712189.3752235528</v>
+      </c>
+      <c r="T54" s="3">
+        <v>86385910.929247499</v>
       </c>
       <c r="U54">
-        <v>94.395728173447182</v>
+        <v>94.827346169157948</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="B55">
-        <v>10</v>
-      </c>
-      <c r="C55">
-        <v>625251.12010516541</v>
+        <v>40</v>
+      </c>
+      <c r="C55" s="2">
+        <v>11285480.33622128</v>
       </c>
       <c r="D55">
-        <v>0.36299999999999999</v>
+        <v>1.452</v>
       </c>
       <c r="E55">
         <v>11.942294831374801</v>
@@ -4937,63 +4977,63 @@
         <v>104.5</v>
       </c>
       <c r="G55">
-        <v>116.80529483137479</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H55">
-        <v>73032641.427531183</v>
-      </c>
-      <c r="I55">
-        <v>6959181.7609870806</v>
+        <v>1330493746.072154</v>
+      </c>
+      <c r="I55" s="3">
+        <v>125609865.2115964</v>
       </c>
       <c r="J55">
-        <v>-66073459.666544102</v>
+        <v>-1204883880.860558</v>
       </c>
       <c r="K55">
         <v>200</v>
       </c>
       <c r="L55">
-        <v>3127</v>
+        <v>56428</v>
       </c>
       <c r="M55">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N55">
-        <v>62540</v>
+        <v>4514240</v>
       </c>
       <c r="O55">
-        <v>18762</v>
+        <v>1354272</v>
       </c>
       <c r="P55">
-        <v>50094.54</v>
-      </c>
-      <c r="Q55">
-        <v>58023303.945759349</v>
+        <v>3615906.24</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>1047292575.201335</v>
       </c>
       <c r="R55">
-        <v>2901165.197287967</v>
-      </c>
-      <c r="S55">
-        <v>2951259.737287967</v>
-      </c>
-      <c r="T55">
-        <v>55072044.20847138</v>
+        <v>52364628.760066733</v>
+      </c>
+      <c r="S55" s="3">
+        <v>55980535.000066727</v>
+      </c>
+      <c r="T55" s="3">
+        <v>991312040.20126796</v>
       </c>
       <c r="U55">
-        <v>94.913664792258601</v>
+        <v>94.654737718416001</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B56">
-        <v>10</v>
-      </c>
-      <c r="C56">
-        <v>611398.32214950491</v>
+        <v>20</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1534972.3896503481</v>
       </c>
       <c r="D56">
-        <v>0.36299999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E56">
         <v>11.942294831374801</v>
@@ -5002,63 +5042,63 @@
         <v>104.5</v>
       </c>
       <c r="G56">
-        <v>116.80529483137479</v>
+        <v>117.16829483137479</v>
       </c>
       <c r="H56">
-        <v>71414561.278080791</v>
-      </c>
-      <c r="I56">
-        <v>6804997.088986082</v>
+        <v>179850097.5085718</v>
+      </c>
+      <c r="I56" s="3">
+        <v>17084578.522429109</v>
       </c>
       <c r="J56">
-        <v>-64609564.189094707</v>
+        <v>-162765518.98614269</v>
       </c>
       <c r="K56">
         <v>200</v>
       </c>
       <c r="L56">
-        <v>3057</v>
+        <v>7675</v>
       </c>
       <c r="M56">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N56">
-        <v>61140</v>
+        <v>307000</v>
       </c>
       <c r="O56">
-        <v>18342</v>
+        <v>92100</v>
       </c>
       <c r="P56">
-        <v>48973.14</v>
-      </c>
-      <c r="Q56">
-        <v>56737764.295474052</v>
+        <v>245907</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>142445437.7595523</v>
       </c>
       <c r="R56">
-        <v>2836888.214773702</v>
-      </c>
-      <c r="S56">
-        <v>2885861.354773703</v>
-      </c>
-      <c r="T56">
-        <v>53851902.940700352</v>
+        <v>7122271.8879776122</v>
+      </c>
+      <c r="S56" s="3">
+        <v>7368178.8879776122</v>
+      </c>
+      <c r="T56" s="3">
+        <v>135077258.8715747</v>
       </c>
       <c r="U56">
-        <v>94.913685107955672</v>
+        <v>94.827367584481664</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B57">
-        <v>10</v>
-      </c>
-      <c r="C57">
-        <v>588996.33817545942</v>
+        <v>30</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1534972.3896503481</v>
       </c>
       <c r="D57">
-        <v>0.36299999999999999</v>
+        <v>1.089</v>
       </c>
       <c r="E57">
         <v>11.942294831374801</v>
@@ -5067,63 +5107,63 @@
         <v>104.5</v>
       </c>
       <c r="G57">
-        <v>116.80529483137479</v>
+        <v>117.53129483137479</v>
       </c>
       <c r="H57">
-        <v>68797890.935184672</v>
-      </c>
-      <c r="I57">
-        <v>6555658.1061852509</v>
+        <v>180407292.4860149</v>
+      </c>
+      <c r="I57" s="3">
+        <v>17084578.522429109</v>
       </c>
       <c r="J57">
-        <v>-62242232.828999422</v>
+        <v>-163322713.96358579</v>
       </c>
       <c r="K57">
         <v>200</v>
       </c>
       <c r="L57">
-        <v>2945</v>
+        <v>7675</v>
       </c>
       <c r="M57">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="N57">
-        <v>58900</v>
+        <v>460500</v>
       </c>
       <c r="O57">
-        <v>17670</v>
+        <v>138150</v>
       </c>
       <c r="P57">
-        <v>47178.9</v>
-      </c>
-      <c r="Q57">
-        <v>54658860.182682633</v>
+        <v>368860.5</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>142445437.7595523</v>
       </c>
       <c r="R57">
-        <v>2732943.009134131</v>
-      </c>
-      <c r="S57">
-        <v>2780121.9091341309</v>
-      </c>
-      <c r="T57">
-        <v>51878738.273548499</v>
+        <v>7122271.8879776122</v>
+      </c>
+      <c r="S57" s="3">
+        <v>7491132.3879776122</v>
+      </c>
+      <c r="T57" s="3">
+        <v>134954305.3715747</v>
       </c>
       <c r="U57">
-        <v>94.913684808204337</v>
+        <v>94.741051376722481</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B58">
-        <v>80</v>
-      </c>
-      <c r="C58">
-        <v>552667.70606108301</v>
+        <v>40</v>
+      </c>
+      <c r="C58" s="2">
+        <v>2077070.866189966</v>
       </c>
       <c r="D58">
-        <v>2.9039999999999999</v>
+        <v>1.452</v>
       </c>
       <c r="E58">
         <v>11.942294831374801</v>
@@ -5132,63 +5172,63 @@
         <v>104.5</v>
       </c>
       <c r="G58">
-        <v>119.34629483137481</v>
+        <v>117.89429483137479</v>
       </c>
       <c r="H58">
-        <v>65958842.991345592</v>
-      </c>
-      <c r="I58">
-        <v>6151312.4826708864</v>
+        <v>244874805.08425891</v>
+      </c>
+      <c r="I58" s="3">
+        <v>23118253.168160029</v>
       </c>
       <c r="J58">
-        <v>-59807530.508674704</v>
+        <v>-221756551.9160988</v>
       </c>
       <c r="K58">
         <v>200</v>
       </c>
       <c r="L58">
-        <v>2764</v>
+        <v>10386</v>
       </c>
       <c r="M58">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="N58">
-        <v>442240</v>
+        <v>830880</v>
       </c>
       <c r="O58">
-        <v>132672</v>
+        <v>249264</v>
       </c>
       <c r="P58">
-        <v>354234.24</v>
-      </c>
-      <c r="Q58">
-        <v>51287563.122468501</v>
+        <v>665534.88</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>192752176.3824288</v>
       </c>
       <c r="R58">
-        <v>2564378.1561234249</v>
-      </c>
-      <c r="S58">
-        <v>2918612.3961234251</v>
-      </c>
-      <c r="T58">
-        <v>48368950.726345077</v>
+        <v>9637608.8191214409</v>
+      </c>
+      <c r="S58" s="3">
+        <v>10303143.69912144</v>
+      </c>
+      <c r="T58" s="3">
+        <v>182449032.68330741</v>
       </c>
       <c r="U58">
-        <v>94.309317467172065</v>
+        <v>94.654719914197202</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B59">
-        <v>10</v>
-      </c>
-      <c r="C59">
-        <v>547838.20988810796</v>
+        <v>70</v>
+      </c>
+      <c r="C59" s="2">
+        <v>637526.94075311639</v>
       </c>
       <c r="D59">
-        <v>0.36299999999999999</v>
+        <v>2.5409999999999999</v>
       </c>
       <c r="E59">
         <v>11.942294831374801</v>
@@ -5197,63 +5237,63 @@
         <v>104.5</v>
       </c>
       <c r="G59">
-        <v>116.80529483137479</v>
+        <v>118.98329483137481</v>
       </c>
       <c r="H59">
-        <v>63990403.625873037</v>
-      </c>
-      <c r="I59">
-        <v>6097559.1336547798</v>
+        <v>75855055.954572454</v>
+      </c>
+      <c r="I59" s="3">
+        <v>7095814.3305376954</v>
       </c>
       <c r="J59">
-        <v>-57892844.492218263</v>
+        <v>-68759241.624034762</v>
       </c>
       <c r="K59">
         <v>200</v>
       </c>
       <c r="L59">
-        <v>2740</v>
+        <v>3188</v>
       </c>
       <c r="M59">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="N59">
-        <v>54800</v>
+        <v>446320</v>
       </c>
       <c r="O59">
-        <v>16440</v>
+        <v>133896</v>
       </c>
       <c r="P59">
-        <v>43894.8</v>
-      </c>
-      <c r="Q59">
-        <v>50839385.87761642</v>
+        <v>357502.32</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>59162500.101889201</v>
       </c>
       <c r="R59">
-        <v>2541969.2938808212</v>
-      </c>
-      <c r="S59">
-        <v>2585864.093880821</v>
-      </c>
-      <c r="T59">
-        <v>48253521.783735603</v>
+        <v>2958125.0050944602</v>
+      </c>
+      <c r="S59" s="3">
+        <v>3315627.32509446</v>
+      </c>
+      <c r="T59" s="3">
+        <v>55846872.776794739</v>
       </c>
       <c r="U59">
-        <v>94.913659853984726</v>
+        <v>94.395728173447182</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="B60">
-        <v>100</v>
-      </c>
-      <c r="C60">
-        <v>509315.28864071658</v>
+        <v>80</v>
+      </c>
+      <c r="C60" s="2">
+        <v>2204600.0579179772</v>
       </c>
       <c r="D60">
-        <v>3.63</v>
+        <v>2.9039999999999999</v>
       </c>
       <c r="E60">
         <v>11.942294831374801</v>
@@ -5262,63 +5302,63 @@
         <v>104.5</v>
       </c>
       <c r="G60">
-        <v>120.0722948313748</v>
+        <v>119.34629483137481</v>
       </c>
       <c r="H60">
-        <v>61154655.499794878</v>
-      </c>
-      <c r="I60">
-        <v>5668790.5920171477</v>
+        <v>263110848.49754491</v>
+      </c>
+      <c r="I60" s="3">
+        <v>24537680.97329171</v>
       </c>
       <c r="J60">
-        <v>-55485864.907777727</v>
+        <v>-238573167.5242531</v>
       </c>
       <c r="K60">
         <v>200</v>
       </c>
       <c r="L60">
-        <v>2547</v>
+        <v>11024</v>
       </c>
       <c r="M60">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="N60">
-        <v>509400</v>
+        <v>1763840</v>
       </c>
       <c r="O60">
-        <v>152820</v>
+        <v>529152</v>
       </c>
       <c r="P60">
-        <v>408029.4</v>
-      </c>
-      <c r="Q60">
-        <v>47264458.785858497</v>
+        <v>1412835.84</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>204586885.37478831</v>
       </c>
       <c r="R60">
-        <v>2363222.9392929249</v>
-      </c>
-      <c r="S60">
-        <v>2771252.3392929249</v>
-      </c>
-      <c r="T60">
-        <v>44493206.446565583</v>
+        <v>10229344.26873941</v>
+      </c>
+      <c r="S60" s="3">
+        <v>11642180.10873941</v>
+      </c>
+      <c r="T60" s="3">
+        <v>192944705.26604891</v>
       </c>
       <c r="U60">
-        <v>94.136709886283342</v>
+        <v>94.309420133450018</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B61">
-        <v>20</v>
-      </c>
-      <c r="C61">
-        <v>494540.6824261822</v>
+        <v>30</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1914110.8310628589</v>
       </c>
       <c r="D61">
-        <v>0.72599999999999998</v>
+        <v>1.089</v>
       </c>
       <c r="E61">
         <v>11.942294831374801</v>
@@ -5327,60 +5367,60 @@
         <v>104.5</v>
       </c>
       <c r="G61">
-        <v>117.16829483137479</v>
+        <v>117.53129483137479</v>
       </c>
       <c r="H61">
-        <v>57944488.484620214</v>
-      </c>
-      <c r="I61">
-        <v>5504345.9924190529</v>
+        <v>224967924.42557669</v>
+      </c>
+      <c r="I61" s="3">
+        <v>21304472.324335821</v>
       </c>
       <c r="J61">
-        <v>-52440142.492201149</v>
+        <v>-203663452.1012409</v>
       </c>
       <c r="K61">
         <v>200</v>
       </c>
       <c r="L61">
-        <v>2473</v>
+        <v>9571</v>
       </c>
       <c r="M61">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N61">
-        <v>98920</v>
+        <v>574260</v>
       </c>
       <c r="O61">
-        <v>29676</v>
+        <v>172278</v>
       </c>
       <c r="P61">
-        <v>79234.92</v>
-      </c>
-      <c r="Q61">
-        <v>45893375.329149708</v>
+        <v>459982.26</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>177629485.12263331</v>
       </c>
       <c r="R61">
-        <v>2294668.766457486</v>
-      </c>
-      <c r="S61">
-        <v>2373903.686457485</v>
-      </c>
-      <c r="T61">
-        <v>43519471.642692223</v>
+        <v>8881474.2561316639</v>
+      </c>
+      <c r="S61" s="3">
+        <v>9341456.5161316637</v>
+      </c>
+      <c r="T61" s="3">
+        <v>168288028.60650161</v>
       </c>
       <c r="U61">
-        <v>94.827349983670359</v>
+        <v>94.741043971566754</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="B62">
         <v>10</v>
       </c>
-      <c r="C62">
-        <v>438270.56791048631</v>
+      <c r="C62" s="2">
+        <v>5007446.6160084549</v>
       </c>
       <c r="D62">
         <v>0.36299999999999999</v>
@@ -5395,60 +5435,60 @@
         <v>116.80529483137479</v>
       </c>
       <c r="H62">
-        <v>51192322.900698423</v>
-      </c>
-      <c r="I62">
-        <v>4878047.3069238234</v>
+        <v>584896278.33523762</v>
+      </c>
+      <c r="I62" s="3">
+        <v>55733976.379572473</v>
       </c>
       <c r="J62">
-        <v>-46314275.593774602</v>
+        <v>-529162301.95566517</v>
       </c>
       <c r="K62">
         <v>200</v>
       </c>
       <c r="L62">
-        <v>2192</v>
+        <v>25038</v>
       </c>
       <c r="M62">
         <v>20</v>
       </c>
       <c r="N62">
-        <v>43840</v>
+        <v>500760</v>
       </c>
       <c r="O62">
-        <v>13152</v>
+        <v>150228</v>
       </c>
       <c r="P62">
-        <v>35115.839999999997</v>
-      </c>
-      <c r="Q62">
-        <v>40671508.702093132</v>
+        <v>401108.76</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>464691045.96558458</v>
       </c>
       <c r="R62">
-        <v>2033575.435104656</v>
-      </c>
-      <c r="S62">
-        <v>2068691.2751046559</v>
-      </c>
-      <c r="T62">
-        <v>38602817.426988482</v>
+        <v>23234552.29827923</v>
+      </c>
+      <c r="S62" s="3">
+        <v>23635661.058279231</v>
+      </c>
+      <c r="T62" s="3">
+        <v>441055384.90730542</v>
       </c>
       <c r="U62">
-        <v>94.913659853984726</v>
+        <v>94.91368270090797</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="B63">
-        <v>40</v>
-      </c>
-      <c r="C63">
-        <v>347648.47067168099</v>
+        <v>70</v>
+      </c>
+      <c r="C63" s="2">
+        <v>3201858.8671254199</v>
       </c>
       <c r="D63">
-        <v>1.452</v>
+        <v>2.5409999999999999</v>
       </c>
       <c r="E63">
         <v>11.942294831374801</v>
@@ -5457,63 +5497,63 @@
         <v>104.5</v>
       </c>
       <c r="G63">
-        <v>117.89429483137479</v>
+        <v>118.98329483137481</v>
       </c>
       <c r="H63">
-        <v>40985771.299043722</v>
-      </c>
-      <c r="I63">
-        <v>3869403.538096</v>
+        <v>380967717.59563547</v>
+      </c>
+      <c r="I63" s="3">
+        <v>35637389.70288635</v>
       </c>
       <c r="J63">
-        <v>-37116367.760947712</v>
+        <v>-345330327.89274919</v>
       </c>
       <c r="K63">
         <v>200</v>
       </c>
       <c r="L63">
-        <v>1739</v>
+        <v>16010</v>
       </c>
       <c r="M63">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="N63">
-        <v>139120</v>
+        <v>2241400</v>
       </c>
       <c r="O63">
-        <v>41736</v>
+        <v>672420</v>
       </c>
       <c r="P63">
-        <v>111435.12</v>
-      </c>
-      <c r="Q63">
-        <v>32261778.078331999</v>
+        <v>1795361.4</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>297132502.86923897</v>
       </c>
       <c r="R63">
-        <v>1613088.9039165999</v>
-      </c>
-      <c r="S63">
-        <v>1724524.0239166</v>
-      </c>
-      <c r="T63">
-        <v>30537254.054415401</v>
+        <v>14856625.14346195</v>
+      </c>
+      <c r="S63" s="3">
+        <v>16651986.54346195</v>
+      </c>
+      <c r="T63" s="3">
+        <v>280480516.32577711</v>
       </c>
       <c r="U63">
-        <v>94.654590891644489</v>
+        <v>94.395770781498769</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B64">
-        <v>10</v>
-      </c>
-      <c r="C64">
-        <v>158253.01837637831</v>
+        <v>100</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1534972.3896503481</v>
       </c>
       <c r="D64">
-        <v>0.36299999999999999</v>
+        <v>3.63</v>
       </c>
       <c r="E64">
         <v>11.942294831374801</v>
@@ -5522,63 +5562,63 @@
         <v>104.5</v>
       </c>
       <c r="G64">
-        <v>116.80529483137479</v>
+        <v>120.0722948313748</v>
       </c>
       <c r="H64">
-        <v>18484790.469407842</v>
-      </c>
-      <c r="I64">
-        <v>1761390.717574097</v>
+        <v>184307657.32811639</v>
+      </c>
+      <c r="I64" s="3">
+        <v>17084578.522429109</v>
       </c>
       <c r="J64">
-        <v>-16723399.751833741</v>
+        <v>-167223078.80568731</v>
       </c>
       <c r="K64">
         <v>200</v>
       </c>
       <c r="L64">
-        <v>792</v>
+        <v>7675</v>
       </c>
       <c r="M64">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="N64">
-        <v>15840</v>
+        <v>1535000</v>
       </c>
       <c r="O64">
-        <v>4752</v>
+        <v>460500</v>
       </c>
       <c r="P64">
-        <v>12687.84</v>
-      </c>
-      <c r="Q64">
-        <v>14685880.1053279</v>
+        <v>1229535</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>142445437.7595523</v>
       </c>
       <c r="R64">
-        <v>734294.00526639516</v>
-      </c>
-      <c r="S64">
-        <v>746981.84526639513</v>
-      </c>
-      <c r="T64">
-        <v>13938898.26006151</v>
+        <v>7122271.8879776122</v>
+      </c>
+      <c r="S64" s="3">
+        <v>8351806.8879776122</v>
+      </c>
+      <c r="T64" s="3">
+        <v>134093630.8715747</v>
       </c>
       <c r="U64">
-        <v>94.913605177837482</v>
+        <v>94.136837922408262</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B65">
-        <v>20</v>
-      </c>
-      <c r="C65">
-        <v>131481.1703731459</v>
+        <v>30</v>
+      </c>
+      <c r="C65" s="2">
+        <v>4186288.3354100399</v>
       </c>
       <c r="D65">
-        <v>0.72599999999999998</v>
+        <v>1.089</v>
       </c>
       <c r="E65">
         <v>11.942294831374801</v>
@@ -5587,52 +5627,57 @@
         <v>104.5</v>
       </c>
       <c r="G65">
-        <v>117.16829483137479</v>
+        <v>117.53129483137479</v>
       </c>
       <c r="H65">
-        <v>15405424.53505498</v>
-      </c>
-      <c r="I65">
-        <v>1463414.1920771471</v>
+        <v>492019888.59822261</v>
+      </c>
+      <c r="I65" s="3">
+        <v>46594305.06117031</v>
       </c>
       <c r="J65">
-        <v>-13942010.342977829</v>
+        <v>-445425583.53705227</v>
       </c>
       <c r="K65">
         <v>200</v>
       </c>
       <c r="L65">
-        <v>658</v>
+        <v>20932</v>
       </c>
       <c r="M65">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N65">
-        <v>26320</v>
+        <v>1255920</v>
       </c>
       <c r="O65">
-        <v>7896</v>
+        <v>376776</v>
       </c>
       <c r="P65">
-        <v>21082.32</v>
-      </c>
-      <c r="Q65">
-        <v>12201452.61062794</v>
+        <v>1005991.92</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>388487557.5260517</v>
       </c>
       <c r="R65">
-        <v>610072.63053139683</v>
-      </c>
-      <c r="S65">
-        <v>631154.95053139678</v>
-      </c>
-      <c r="T65">
-        <v>11570297.660096539</v>
+        <v>19424377.876302589</v>
+      </c>
+      <c r="S65" s="3">
+        <v>20430369.796302591</v>
+      </c>
+      <c r="T65" s="3">
+        <v>368057187.72974908</v>
       </c>
       <c r="U65">
-        <v>94.827214671295465</v>
+        <v>94.741049127440178</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U65" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U65">
+      <sortCondition ref="A1:A65"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Resultados_planta_custos_emissoes_hubs.xlsx
+++ b/Resultados_planta_custos_emissoes_hubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epegovbr-my.sharepoint.com/personal/otto_hebeda_epe_gov_br/Documents/Documentos/Resíduos - projetos/Residuos na produção de cimento/Código/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_88B55A31088DCF73299E7AD3AB8741A67D8A8A46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FDB0AC7-46E5-43DA-9198-EB36E7C13FA3}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_88B55A31088DCF73299E7AD3AB8741A67D8A8A46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{967E8E64-8B2F-43A2-82AC-DF74BDC29194}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23640" yWindow="1560" windowWidth="18900" windowHeight="10965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raio" sheetId="1" r:id="rId1"/>
@@ -533,7 +533,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -599,7 +599,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1445,6 +1445,7 @@
     <col min="17" max="17" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="27" customWidth="1"/>
     <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
